--- a/01_Input/00_CO Validation/Sri Lanka - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Sri Lanka - Energy Projects.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27002"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27004"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="311" documentId="11_59392953A5B08644DD0FF8ADE13F31B695A83B27" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB389C82-BAF1-437B-910C-BCBA62312163}"/>
+  <xr:revisionPtr revIDLastSave="312" documentId="11_59392953A5B08644DD0FF8ADE13F31B695A83B27" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{216CF3CF-FBFF-4B84-8B33-7C88F3D9DE29}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,6 +15,9 @@
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -31,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="117">
   <si>
     <t>Project ID</t>
   </si>
@@ -72,7 +75,7 @@
     <t>Category</t>
   </si>
   <si>
-    <t>Comments</t>
+    <t>Tag</t>
   </si>
   <si>
     <t>SEH Taxonomy</t>
@@ -257,6 +260,9 @@
   </si>
   <si>
     <t>Number of green/sustainable jobs created</t>
+  </si>
+  <si>
+    <t>Comments</t>
   </si>
   <si>
     <t>Around 1.2 million farmers will benefit from five provinces from the energy plans that has RE and EE</t>
@@ -621,17 +627,26 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -642,8 +657,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -656,15 +671,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1090,16 +1096,16 @@
       </c>
     </row>
     <row r="3" spans="1:19">
-      <c r="A3" s="25">
+      <c r="A3" s="23">
         <v>119366</v>
       </c>
-      <c r="B3" s="25" t="s">
+      <c r="B3" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="30" t="s">
+      <c r="C3" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="25">
+      <c r="D3" s="23">
         <v>1007201</v>
       </c>
       <c r="E3" s="14" t="s">
@@ -1118,11 +1124,11 @@
       <c r="J3" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="K3" s="27" t="s">
+      <c r="K3" s="30" t="s">
         <v>33</v>
       </c>
       <c r="L3" s="12"/>
-      <c r="M3" s="27" t="s">
+      <c r="M3" s="30" t="s">
         <v>25</v>
       </c>
       <c r="N3" s="12"/>
@@ -1134,10 +1140,10 @@
       </c>
     </row>
     <row r="4" spans="1:19">
-      <c r="A4" s="25"/>
-      <c r="B4" s="25"/>
-      <c r="C4" s="30"/>
-      <c r="D4" s="25"/>
+      <c r="A4" s="23"/>
+      <c r="B4" s="23"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="23"/>
       <c r="E4" s="14" t="s">
         <v>34</v>
       </c>
@@ -1152,9 +1158,9 @@
       </c>
       <c r="I4" s="14"/>
       <c r="J4" s="14"/>
-      <c r="K4" s="28"/>
+      <c r="K4" s="31"/>
       <c r="L4" s="12"/>
-      <c r="M4" s="28"/>
+      <c r="M4" s="31"/>
       <c r="N4" s="12"/>
       <c r="O4" t="s">
         <v>26</v>
@@ -1170,10 +1176,10 @@
       </c>
     </row>
     <row r="5" spans="1:19">
-      <c r="A5" s="25"/>
-      <c r="B5" s="25"/>
-      <c r="C5" s="30"/>
-      <c r="D5" s="25"/>
+      <c r="A5" s="23"/>
+      <c r="B5" s="23"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="23"/>
       <c r="E5" s="14" t="s">
         <v>34</v>
       </c>
@@ -1192,9 +1198,9 @@
       <c r="J5" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="K5" s="29"/>
+      <c r="K5" s="32"/>
       <c r="L5" s="12"/>
-      <c r="M5" s="29"/>
+      <c r="M5" s="32"/>
       <c r="N5" s="12"/>
       <c r="O5" t="s">
         <v>26</v>
@@ -1210,16 +1216,16 @@
       </c>
     </row>
     <row r="6" spans="1:19">
-      <c r="A6" s="25">
+      <c r="A6" s="23">
         <v>134410</v>
       </c>
-      <c r="B6" s="25" t="s">
+      <c r="B6" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="30" t="s">
+      <c r="C6" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="D6" s="25">
+      <c r="D6" s="23">
         <v>261353</v>
       </c>
       <c r="E6" s="14" t="s">
@@ -1237,11 +1243,11 @@
       <c r="J6" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="K6" s="27" t="s">
+      <c r="K6" s="30" t="s">
         <v>45</v>
       </c>
       <c r="L6" s="12"/>
-      <c r="M6" s="27" t="s">
+      <c r="M6" s="30" t="s">
         <v>25</v>
       </c>
       <c r="N6" s="12"/>
@@ -1253,10 +1259,10 @@
       </c>
     </row>
     <row r="7" spans="1:19">
-      <c r="A7" s="25"/>
-      <c r="B7" s="25"/>
-      <c r="C7" s="30"/>
-      <c r="D7" s="25"/>
+      <c r="A7" s="23"/>
+      <c r="B7" s="23"/>
+      <c r="C7" s="29"/>
+      <c r="D7" s="23"/>
       <c r="E7" s="14" t="s">
         <v>30</v>
       </c>
@@ -1273,9 +1279,9 @@
       <c r="J7" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="K7" s="28"/>
+      <c r="K7" s="31"/>
       <c r="L7" s="12"/>
-      <c r="M7" s="28"/>
+      <c r="M7" s="31"/>
       <c r="N7" s="12"/>
       <c r="O7" t="s">
         <v>26</v>
@@ -1285,10 +1291,10 @@
       </c>
     </row>
     <row r="8" spans="1:19">
-      <c r="A8" s="25"/>
-      <c r="B8" s="25"/>
-      <c r="C8" s="30"/>
-      <c r="D8" s="25"/>
+      <c r="A8" s="23"/>
+      <c r="B8" s="23"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="23"/>
       <c r="E8" s="14" t="s">
         <v>34</v>
       </c>
@@ -1305,9 +1311,9 @@
       <c r="J8" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="K8" s="29"/>
+      <c r="K8" s="32"/>
       <c r="L8" s="12"/>
-      <c r="M8" s="29"/>
+      <c r="M8" s="32"/>
       <c r="N8" s="12"/>
       <c r="O8" t="s">
         <v>26</v>
@@ -1323,16 +1329,16 @@
       </c>
     </row>
     <row r="9" spans="1:19" ht="30.75">
-      <c r="A9" s="25">
+      <c r="A9" s="23">
         <v>142290</v>
       </c>
-      <c r="B9" s="25" t="s">
+      <c r="B9" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="C9" s="30" t="s">
+      <c r="C9" s="29" t="s">
         <v>51</v>
       </c>
-      <c r="D9" s="25">
+      <c r="D9" s="23">
         <v>324000</v>
       </c>
       <c r="E9" s="14" t="s">
@@ -1351,11 +1357,11 @@
       <c r="J9" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="K9" s="27" t="s">
+      <c r="K9" s="30" t="s">
         <v>54</v>
       </c>
       <c r="L9" s="12"/>
-      <c r="M9" s="27" t="s">
+      <c r="M9" s="30" t="s">
         <v>25</v>
       </c>
       <c r="N9" s="12"/>
@@ -1373,10 +1379,10 @@
       </c>
     </row>
     <row r="10" spans="1:19">
-      <c r="A10" s="25"/>
-      <c r="B10" s="25"/>
-      <c r="C10" s="30"/>
-      <c r="D10" s="25"/>
+      <c r="A10" s="23"/>
+      <c r="B10" s="23"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="23"/>
       <c r="E10" s="14" t="s">
         <v>34</v>
       </c>
@@ -1393,9 +1399,9 @@
       <c r="J10" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="K10" s="28"/>
+      <c r="K10" s="31"/>
       <c r="L10" s="12"/>
-      <c r="M10" s="28"/>
+      <c r="M10" s="31"/>
       <c r="N10" s="12"/>
       <c r="O10" t="s">
         <v>26</v>
@@ -1411,10 +1417,10 @@
       </c>
     </row>
     <row r="11" spans="1:19">
-      <c r="A11" s="25"/>
-      <c r="B11" s="25"/>
-      <c r="C11" s="30"/>
-      <c r="D11" s="25"/>
+      <c r="A11" s="23"/>
+      <c r="B11" s="23"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="23"/>
       <c r="E11" s="14" t="s">
         <v>34</v>
       </c>
@@ -1431,9 +1437,9 @@
       <c r="J11" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="K11" s="29"/>
+      <c r="K11" s="32"/>
       <c r="L11" s="12"/>
-      <c r="M11" s="29"/>
+      <c r="M11" s="32"/>
       <c r="N11" s="22"/>
       <c r="O11" t="s">
         <v>26</v>
@@ -1449,16 +1455,16 @@
       </c>
     </row>
     <row r="12" spans="1:19" ht="17.25" customHeight="1">
-      <c r="A12" s="25">
+      <c r="A12" s="23">
         <v>145829</v>
       </c>
-      <c r="B12" s="25" t="s">
+      <c r="B12" s="23" t="s">
         <v>60</v>
       </c>
-      <c r="C12" s="30" t="s">
+      <c r="C12" s="29" t="s">
         <v>61</v>
       </c>
-      <c r="D12" s="25">
+      <c r="D12" s="23">
         <v>1151772</v>
       </c>
       <c r="E12" s="14" t="s">
@@ -1477,11 +1483,11 @@
       <c r="J12" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="K12" s="23" t="s">
+      <c r="K12" s="27" t="s">
         <v>24</v>
       </c>
       <c r="L12" s="12"/>
-      <c r="M12" s="23" t="s">
+      <c r="M12" s="27" t="s">
         <v>25</v>
       </c>
       <c r="N12" s="12"/>
@@ -1493,10 +1499,10 @@
       </c>
     </row>
     <row r="13" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A13" s="25"/>
-      <c r="B13" s="25"/>
-      <c r="C13" s="30"/>
-      <c r="D13" s="25"/>
+      <c r="A13" s="23"/>
+      <c r="B13" s="23"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="23"/>
       <c r="E13" s="14" t="s">
         <v>34</v>
       </c>
@@ -1513,9 +1519,9 @@
       <c r="J13" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="K13" s="24"/>
+      <c r="K13" s="28"/>
       <c r="L13" s="12"/>
-      <c r="M13" s="24"/>
+      <c r="M13" s="28"/>
       <c r="N13" s="12"/>
       <c r="O13" t="s">
         <v>26</v>
@@ -1531,14 +1537,14 @@
       </c>
     </row>
     <row r="14" spans="1:19">
-      <c r="A14" s="25">
+      <c r="A14" s="23">
         <v>100344</v>
       </c>
-      <c r="B14" s="25" t="s">
+      <c r="B14" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="C14" s="35"/>
-      <c r="D14" s="35"/>
+      <c r="C14" s="24"/>
+      <c r="D14" s="24"/>
       <c r="E14" s="17" t="s">
         <v>69</v>
       </c>
@@ -1555,7 +1561,7 @@
       <c r="J14" s="21"/>
       <c r="K14" s="12"/>
       <c r="L14" s="12"/>
-      <c r="M14" s="23" t="s">
+      <c r="M14" s="27" t="s">
         <v>25</v>
       </c>
       <c r="N14" s="12"/>
@@ -1567,10 +1573,10 @@
       </c>
     </row>
     <row r="15" spans="1:19">
-      <c r="A15" s="25"/>
-      <c r="B15" s="25"/>
-      <c r="C15" s="36"/>
-      <c r="D15" s="36"/>
+      <c r="A15" s="23"/>
+      <c r="B15" s="23"/>
+      <c r="C15" s="25"/>
+      <c r="D15" s="25"/>
       <c r="E15" s="17" t="s">
         <v>30</v>
       </c>
@@ -1589,7 +1595,7 @@
       </c>
       <c r="K15" s="12"/>
       <c r="L15" s="12"/>
-      <c r="M15" s="24"/>
+      <c r="M15" s="28"/>
       <c r="N15" s="12"/>
       <c r="O15" t="s">
         <v>26</v>
@@ -1599,10 +1605,10 @@
       </c>
     </row>
     <row r="16" spans="1:19">
-      <c r="A16" s="25"/>
-      <c r="B16" s="25"/>
-      <c r="C16" s="37"/>
-      <c r="D16" s="37"/>
+      <c r="A16" s="23"/>
+      <c r="B16" s="23"/>
+      <c r="C16" s="26"/>
+      <c r="D16" s="26"/>
       <c r="E16" s="17" t="s">
         <v>73</v>
       </c>
@@ -1630,16 +1636,18 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="C14:C16"/>
-    <mergeCell ref="D14:D16"/>
-    <mergeCell ref="M14:M15"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="K12:K13"/>
+    <mergeCell ref="M6:M8"/>
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="B3:B5"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="K3:K5"/>
+    <mergeCell ref="M3:M5"/>
+    <mergeCell ref="A6:A8"/>
+    <mergeCell ref="B6:B8"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="K6:K8"/>
     <mergeCell ref="M12:M13"/>
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="B9:B11"/>
@@ -1647,18 +1655,16 @@
     <mergeCell ref="D9:D11"/>
     <mergeCell ref="K9:K11"/>
     <mergeCell ref="M9:M11"/>
-    <mergeCell ref="A6:A8"/>
-    <mergeCell ref="B6:B8"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="K6:K8"/>
-    <mergeCell ref="M6:M8"/>
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="B3:B5"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="K3:K5"/>
-    <mergeCell ref="M3:M5"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="K12:K13"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="D14:D16"/>
+    <mergeCell ref="M14:M15"/>
   </mergeCells>
   <dataValidations count="6">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S16" xr:uid="{2656783B-E017-4B69-B2BF-55ABED0028FD}">
@@ -1758,7 +1764,7 @@
         <v>12</v>
       </c>
       <c r="N1" s="10" t="s">
-        <v>13</v>
+        <v>75</v>
       </c>
       <c r="O1" s="9" t="s">
         <v>14</v>
@@ -1821,16 +1827,16 @@
       </c>
     </row>
     <row r="3" spans="1:19">
-      <c r="A3" s="25">
+      <c r="A3" s="23">
         <v>119366</v>
       </c>
-      <c r="B3" s="25" t="s">
+      <c r="B3" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="30" t="s">
+      <c r="C3" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="25">
+      <c r="D3" s="23">
         <v>1007201</v>
       </c>
       <c r="E3" s="14" t="s">
@@ -1849,11 +1855,11 @@
       <c r="J3" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="K3" s="27" t="s">
+      <c r="K3" s="30" t="s">
         <v>33</v>
       </c>
       <c r="L3" s="12"/>
-      <c r="M3" s="27" t="s">
+      <c r="M3" s="30" t="s">
         <v>25</v>
       </c>
       <c r="N3" s="12"/>
@@ -1865,10 +1871,10 @@
       </c>
     </row>
     <row r="4" spans="1:19">
-      <c r="A4" s="25"/>
-      <c r="B4" s="25"/>
-      <c r="C4" s="30"/>
-      <c r="D4" s="25"/>
+      <c r="A4" s="23"/>
+      <c r="B4" s="23"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="23"/>
       <c r="E4" s="14" t="s">
         <v>34</v>
       </c>
@@ -1883,9 +1889,9 @@
       </c>
       <c r="I4" s="14"/>
       <c r="J4" s="14"/>
-      <c r="K4" s="28"/>
+      <c r="K4" s="31"/>
       <c r="L4" s="12"/>
-      <c r="M4" s="28"/>
+      <c r="M4" s="31"/>
       <c r="N4" s="12"/>
       <c r="O4" t="s">
         <v>26</v>
@@ -1901,10 +1907,10 @@
       </c>
     </row>
     <row r="5" spans="1:19">
-      <c r="A5" s="25"/>
-      <c r="B5" s="25"/>
-      <c r="C5" s="30"/>
-      <c r="D5" s="25"/>
+      <c r="A5" s="23"/>
+      <c r="B5" s="23"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="23"/>
       <c r="E5" s="14" t="s">
         <v>34</v>
       </c>
@@ -1921,11 +1927,11 @@
         <v>1200000</v>
       </c>
       <c r="J5" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="K5" s="29"/>
+        <v>76</v>
+      </c>
+      <c r="K5" s="32"/>
       <c r="L5" s="12"/>
-      <c r="M5" s="29"/>
+      <c r="M5" s="32"/>
       <c r="N5" s="12"/>
       <c r="O5" t="s">
         <v>26</v>
@@ -1941,16 +1947,16 @@
       </c>
     </row>
     <row r="6" spans="1:19">
-      <c r="A6" s="25">
+      <c r="A6" s="23">
         <v>134410</v>
       </c>
-      <c r="B6" s="25" t="s">
+      <c r="B6" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="30" t="s">
+      <c r="C6" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="D6" s="25">
+      <c r="D6" s="23">
         <v>261353</v>
       </c>
       <c r="E6" s="14" t="s">
@@ -1968,11 +1974,11 @@
       <c r="J6" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="K6" s="27" t="s">
+      <c r="K6" s="30" t="s">
         <v>45</v>
       </c>
       <c r="L6" s="12"/>
-      <c r="M6" s="27" t="s">
+      <c r="M6" s="30" t="s">
         <v>25</v>
       </c>
       <c r="N6" s="12"/>
@@ -1984,10 +1990,10 @@
       </c>
     </row>
     <row r="7" spans="1:19">
-      <c r="A7" s="25"/>
-      <c r="B7" s="25"/>
-      <c r="C7" s="30"/>
-      <c r="D7" s="25"/>
+      <c r="A7" s="23"/>
+      <c r="B7" s="23"/>
+      <c r="C7" s="29"/>
+      <c r="D7" s="23"/>
       <c r="E7" s="14" t="s">
         <v>30</v>
       </c>
@@ -2004,9 +2010,9 @@
       <c r="J7" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="K7" s="28"/>
+      <c r="K7" s="31"/>
       <c r="L7" s="12"/>
-      <c r="M7" s="28"/>
+      <c r="M7" s="31"/>
       <c r="N7" s="12"/>
       <c r="O7" t="s">
         <v>26</v>
@@ -2016,10 +2022,10 @@
       </c>
     </row>
     <row r="8" spans="1:19">
-      <c r="A8" s="25"/>
-      <c r="B8" s="25"/>
-      <c r="C8" s="30"/>
-      <c r="D8" s="25"/>
+      <c r="A8" s="23"/>
+      <c r="B8" s="23"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="23"/>
       <c r="E8" s="14" t="s">
         <v>34</v>
       </c>
@@ -2036,9 +2042,9 @@
       <c r="J8" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="K8" s="29"/>
+      <c r="K8" s="32"/>
       <c r="L8" s="12"/>
-      <c r="M8" s="29"/>
+      <c r="M8" s="32"/>
       <c r="N8" s="12"/>
       <c r="O8" t="s">
         <v>26</v>
@@ -2054,16 +2060,16 @@
       </c>
     </row>
     <row r="9" spans="1:19" ht="30.75">
-      <c r="A9" s="25">
+      <c r="A9" s="23">
         <v>142290</v>
       </c>
-      <c r="B9" s="25" t="s">
+      <c r="B9" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="C9" s="30" t="s">
+      <c r="C9" s="29" t="s">
         <v>51</v>
       </c>
-      <c r="D9" s="25">
+      <c r="D9" s="23">
         <v>324000</v>
       </c>
       <c r="E9" s="14" t="s">
@@ -2082,11 +2088,11 @@
       <c r="J9" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="K9" s="27" t="s">
+      <c r="K9" s="30" t="s">
         <v>54</v>
       </c>
       <c r="L9" s="12"/>
-      <c r="M9" s="27" t="s">
+      <c r="M9" s="30" t="s">
         <v>25</v>
       </c>
       <c r="N9" s="12"/>
@@ -2104,10 +2110,10 @@
       </c>
     </row>
     <row r="10" spans="1:19">
-      <c r="A10" s="25"/>
-      <c r="B10" s="25"/>
-      <c r="C10" s="30"/>
-      <c r="D10" s="25"/>
+      <c r="A10" s="23"/>
+      <c r="B10" s="23"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="23"/>
       <c r="E10" s="14" t="s">
         <v>34</v>
       </c>
@@ -2124,9 +2130,9 @@
       <c r="J10" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="K10" s="28"/>
+      <c r="K10" s="31"/>
       <c r="L10" s="12"/>
-      <c r="M10" s="28"/>
+      <c r="M10" s="31"/>
       <c r="N10" s="12"/>
       <c r="O10" t="s">
         <v>26</v>
@@ -2142,10 +2148,10 @@
       </c>
     </row>
     <row r="11" spans="1:19">
-      <c r="A11" s="25"/>
-      <c r="B11" s="25"/>
-      <c r="C11" s="30"/>
-      <c r="D11" s="25"/>
+      <c r="A11" s="23"/>
+      <c r="B11" s="23"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="23"/>
       <c r="E11" s="14" t="s">
         <v>34</v>
       </c>
@@ -2162,9 +2168,9 @@
       <c r="J11" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="K11" s="29"/>
+      <c r="K11" s="32"/>
       <c r="L11" s="12"/>
-      <c r="M11" s="29"/>
+      <c r="M11" s="32"/>
       <c r="N11" s="22"/>
       <c r="O11" t="s">
         <v>26</v>
@@ -2180,16 +2186,16 @@
       </c>
     </row>
     <row r="12" spans="1:19" ht="17.25" customHeight="1">
-      <c r="A12" s="25">
+      <c r="A12" s="23">
         <v>145829</v>
       </c>
-      <c r="B12" s="25" t="s">
+      <c r="B12" s="23" t="s">
         <v>60</v>
       </c>
-      <c r="C12" s="30" t="s">
+      <c r="C12" s="29" t="s">
         <v>61</v>
       </c>
-      <c r="D12" s="25">
+      <c r="D12" s="23">
         <v>1151772</v>
       </c>
       <c r="E12" s="14" t="s">
@@ -2208,11 +2214,11 @@
       <c r="J12" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="K12" s="23" t="s">
+      <c r="K12" s="27" t="s">
         <v>24</v>
       </c>
       <c r="L12" s="12"/>
-      <c r="M12" s="23" t="s">
+      <c r="M12" s="27" t="s">
         <v>25</v>
       </c>
       <c r="N12" s="12"/>
@@ -2224,10 +2230,10 @@
       </c>
     </row>
     <row r="13" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A13" s="25"/>
-      <c r="B13" s="25"/>
-      <c r="C13" s="30"/>
-      <c r="D13" s="25"/>
+      <c r="A13" s="23"/>
+      <c r="B13" s="23"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="23"/>
       <c r="E13" s="14" t="s">
         <v>34</v>
       </c>
@@ -2244,9 +2250,9 @@
       <c r="J13" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="K13" s="24"/>
+      <c r="K13" s="28"/>
       <c r="L13" s="12"/>
-      <c r="M13" s="24"/>
+      <c r="M13" s="28"/>
       <c r="N13" s="12"/>
       <c r="O13" t="s">
         <v>26</v>
@@ -2262,14 +2268,14 @@
       </c>
     </row>
     <row r="14" spans="1:19">
-      <c r="A14" s="25">
+      <c r="A14" s="23">
         <v>100344</v>
       </c>
-      <c r="B14" s="25" t="s">
+      <c r="B14" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="C14" s="23"/>
-      <c r="D14" s="23"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="27"/>
       <c r="E14" s="17" t="s">
         <v>69</v>
       </c>
@@ -2286,7 +2292,7 @@
       <c r="J14" s="21"/>
       <c r="K14" s="12"/>
       <c r="L14" s="12"/>
-      <c r="M14" s="23" t="s">
+      <c r="M14" s="27" t="s">
         <v>25</v>
       </c>
       <c r="N14" s="12"/>
@@ -2298,10 +2304,10 @@
       </c>
     </row>
     <row r="15" spans="1:19">
-      <c r="A15" s="25"/>
-      <c r="B15" s="25"/>
-      <c r="C15" s="26"/>
-      <c r="D15" s="26"/>
+      <c r="A15" s="23"/>
+      <c r="B15" s="23"/>
+      <c r="C15" s="33"/>
+      <c r="D15" s="33"/>
       <c r="E15" s="17" t="s">
         <v>30</v>
       </c>
@@ -2320,7 +2326,7 @@
       </c>
       <c r="K15" s="12"/>
       <c r="L15" s="12"/>
-      <c r="M15" s="24"/>
+      <c r="M15" s="28"/>
       <c r="N15" s="12"/>
       <c r="O15" t="s">
         <v>26</v>
@@ -2330,10 +2336,10 @@
       </c>
     </row>
     <row r="16" spans="1:19">
-      <c r="A16" s="25"/>
-      <c r="B16" s="25"/>
-      <c r="C16" s="24"/>
-      <c r="D16" s="24"/>
+      <c r="A16" s="23"/>
+      <c r="B16" s="23"/>
+      <c r="C16" s="28"/>
+      <c r="D16" s="28"/>
       <c r="E16" s="17" t="s">
         <v>73</v>
       </c>
@@ -2361,6 +2367,27 @@
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="K12:K13"/>
+    <mergeCell ref="M12:M13"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="D14:D16"/>
+    <mergeCell ref="M14:M15"/>
+    <mergeCell ref="K3:K5"/>
+    <mergeCell ref="M3:M5"/>
+    <mergeCell ref="K6:K8"/>
+    <mergeCell ref="M6:M8"/>
+    <mergeCell ref="K9:K11"/>
+    <mergeCell ref="M9:M11"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="D9:D11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D13"/>
     <mergeCell ref="A3:A5"/>
     <mergeCell ref="B3:B5"/>
     <mergeCell ref="C3:C5"/>
@@ -2369,27 +2396,6 @@
     <mergeCell ref="B6:B8"/>
     <mergeCell ref="C6:C8"/>
     <mergeCell ref="D6:D8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:B11"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="D9:D11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="K3:K5"/>
-    <mergeCell ref="M3:M5"/>
-    <mergeCell ref="K6:K8"/>
-    <mergeCell ref="M6:M8"/>
-    <mergeCell ref="K9:K11"/>
-    <mergeCell ref="M9:M11"/>
-    <mergeCell ref="K12:K13"/>
-    <mergeCell ref="M12:M13"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="C14:C16"/>
-    <mergeCell ref="D14:D16"/>
-    <mergeCell ref="M14:M15"/>
   </mergeCells>
   <dataValidations count="6">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E12" xr:uid="{8A6EECDF-213D-4435-9AB2-44F0897711E3}"/>
@@ -2523,7 +2529,7 @@
         <v>69</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G3" s="3">
         <v>0</v>
@@ -2588,7 +2594,7 @@
         <v>5</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -2608,7 +2614,7 @@
         <v>30</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G6" s="3">
         <v>0</v>
@@ -2637,7 +2643,7 @@
         <v>30</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G7" s="3">
         <v>0</v>
@@ -2666,7 +2672,7 @@
         <v>30</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G8" s="3">
         <v>0</v>
@@ -2704,7 +2710,7 @@
         <v>3</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -2724,7 +2730,7 @@
         <v>30</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G10" s="3">
         <v>0</v>
@@ -2750,7 +2756,7 @@
         <v>324000</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>58</v>
@@ -2779,10 +2785,10 @@
         <v>1151772</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G12" s="3">
         <v>0</v>
@@ -2855,7 +2861,7 @@
         <v>30</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G15" s="6">
         <v>0</v>
@@ -2875,7 +2881,7 @@
         <v>68</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>74</v>
@@ -2929,160 +2935,160 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="31" t="s">
-        <v>89</v>
+      <c r="A2" s="34" t="s">
+        <v>90</v>
       </c>
       <c r="B2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="31"/>
+      <c r="A3" s="34"/>
       <c r="B3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="31"/>
+      <c r="A4" s="34"/>
       <c r="B4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="32" t="s">
-        <v>96</v>
+      <c r="A5" s="35" t="s">
+        <v>97</v>
       </c>
       <c r="B5" t="s">
         <v>69</v>
       </c>
       <c r="C5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="32"/>
+      <c r="A6" s="35"/>
       <c r="B6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="32"/>
+      <c r="A7" s="35"/>
       <c r="B7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="32"/>
+      <c r="A8" s="35"/>
       <c r="B8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="32"/>
+      <c r="A9" s="35"/>
       <c r="B9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="33" t="s">
-        <v>105</v>
+      <c r="A10" s="36" t="s">
+        <v>106</v>
       </c>
       <c r="B10" t="s">
         <v>21</v>
       </c>
       <c r="C10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="33"/>
+      <c r="A11" s="36"/>
       <c r="B11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="34" t="s">
-        <v>108</v>
+      <c r="A12" s="37" t="s">
+        <v>109</v>
       </c>
       <c r="B12" t="s">
         <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="34"/>
+      <c r="A13" s="37"/>
       <c r="B13" t="s">
         <v>73</v>
       </c>
       <c r="C13" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="34"/>
+      <c r="A14" s="37"/>
       <c r="B14" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C14" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B15" t="s">
         <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="5" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B16" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C16" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -3106,17 +3112,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0d2b1cfbe0bead55dc04bff20486709a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3ed273af6605fa6a207dd3965c2d078" ns2:_="" ns3:_="">
     <xsd:import namespace="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
@@ -3365,14 +3360,25 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{60C138E8-386B-4289-AC99-AD84197522D7}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{36D75D5F-5916-4E44-9F19-6C353537A8C9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD35035E-53EF-4346-8B10-4ECA462E02DA}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD35035E-53EF-4346-8B10-4ECA462E02DA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{36D75D5F-5916-4E44-9F19-6C353537A8C9}"/>
 </file>
--- a/01_Input/00_CO Validation/Sri Lanka - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Sri Lanka - Energy Projects.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27307"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27504"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="423" documentId="11_59392953A5B08644DD0FF8ADE13F31B695A83B27" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C610463C-350B-4452-A125-1714F78076EC}"/>
+  <xr:revisionPtr revIDLastSave="426" documentId="11_59392953A5B08644DD0FF8ADE13F31B695A83B27" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B94C4284-A51B-486B-9BCA-CB86E1466A18}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="142">
   <si>
     <t>Project ID</t>
   </si>
@@ -117,13 +117,10 @@
     <t>UNDP</t>
   </si>
   <si>
-    <t>VF</t>
+    <t>Non-VF</t>
   </si>
   <si>
     <t>Accelerating just energy transition</t>
-  </si>
-  <si>
-    <t>Non-VF</t>
   </si>
   <si>
     <t>Renewable Energy</t>
@@ -751,13 +748,43 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -766,14 +793,8 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -790,30 +811,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1260,14 +1257,14 @@
       <c r="T2" s="21"/>
       <c r="U2" s="33"/>
       <c r="W2" s="10" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="X2" s="10"/>
       <c r="Y2" s="10" t="s">
         <v>28</v>
       </c>
       <c r="Z2" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA2" s="21"/>
       <c r="AB2" s="10"/>
@@ -1276,23 +1273,23 @@
       <c r="AE2" s="14"/>
     </row>
     <row r="3" spans="1:31" ht="45.75">
-      <c r="A3" s="34">
+      <c r="A3" s="43">
         <v>119366</v>
       </c>
-      <c r="B3" s="35" t="s">
+      <c r="B3" s="44" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="40" t="s">
+      <c r="D3" s="43">
+        <v>1007201</v>
+      </c>
+      <c r="E3" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="D3" s="34">
-        <v>1007201</v>
-      </c>
-      <c r="E3" s="12" t="s">
+      <c r="F3" s="12" t="s">
         <v>33</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>34</v>
       </c>
       <c r="G3" s="12">
         <v>0</v>
@@ -1301,10 +1298,10 @@
         <v>273</v>
       </c>
       <c r="I3" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="J3" s="43" t="s">
         <v>35</v>
-      </c>
-      <c r="J3" s="34" t="s">
-        <v>36</v>
       </c>
       <c r="K3" s="10"/>
       <c r="L3" s="26" t="s">
@@ -1321,15 +1318,15 @@
       <c r="S3" s="33"/>
       <c r="T3" s="21"/>
       <c r="U3" s="33"/>
-      <c r="W3" s="34" t="s">
-        <v>29</v>
+      <c r="W3" s="43" t="s">
+        <v>27</v>
       </c>
       <c r="X3" s="10"/>
       <c r="Y3" s="10" t="s">
         <v>28</v>
       </c>
       <c r="Z3" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA3" s="21"/>
       <c r="AB3" s="10"/>
@@ -1338,15 +1335,15 @@
       <c r="AE3" s="12"/>
     </row>
     <row r="4" spans="1:31" ht="45.75">
-      <c r="A4" s="34"/>
-      <c r="B4" s="35"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="34"/>
+      <c r="A4" s="43"/>
+      <c r="B4" s="44"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="43"/>
       <c r="E4" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G4" s="12">
         <v>0</v>
@@ -1355,7 +1352,7 @@
         <v>125</v>
       </c>
       <c r="I4" s="12"/>
-      <c r="J4" s="34"/>
+      <c r="J4" s="43"/>
       <c r="K4" s="10"/>
       <c r="L4" s="26" t="s">
         <v>27</v>
@@ -1371,34 +1368,34 @@
       <c r="S4" s="33"/>
       <c r="T4" s="21"/>
       <c r="U4" s="33"/>
-      <c r="W4" s="34"/>
+      <c r="W4" s="43"/>
       <c r="X4" s="10"/>
       <c r="Y4" s="10" t="s">
         <v>28</v>
       </c>
       <c r="Z4" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA4" s="21"/>
       <c r="AB4" s="10"/>
       <c r="AC4" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="AD4" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AD4" s="10" t="s">
-        <v>39</v>
-      </c>
       <c r="AE4" s="12"/>
     </row>
     <row r="5" spans="1:31" ht="45.75">
-      <c r="A5" s="34"/>
-      <c r="B5" s="35"/>
-      <c r="C5" s="40"/>
-      <c r="D5" s="34"/>
+      <c r="A5" s="43"/>
+      <c r="B5" s="44"/>
+      <c r="C5" s="45"/>
+      <c r="D5" s="43"/>
       <c r="E5" s="12" t="s">
         <v>19</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G5" s="12">
         <v>0</v>
@@ -1407,9 +1404,9 @@
         <v>5</v>
       </c>
       <c r="I5" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="J5" s="34"/>
+        <v>40</v>
+      </c>
+      <c r="J5" s="43"/>
       <c r="K5" s="10"/>
       <c r="L5" s="26" t="s">
         <v>27</v>
@@ -1419,62 +1416,62 @@
         <v>28</v>
       </c>
       <c r="O5" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P5" s="21"/>
       <c r="Q5" s="21" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R5" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S5" s="33"/>
       <c r="T5" s="21" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="U5" s="33">
         <v>1200000</v>
       </c>
-      <c r="W5" s="34"/>
+      <c r="W5" s="43"/>
       <c r="X5" s="10"/>
       <c r="Y5" s="10" t="s">
         <v>28</v>
       </c>
       <c r="Z5" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA5" s="21" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AB5" s="10"/>
       <c r="AC5" s="10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AD5" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AE5" s="12">
         <v>1200000</v>
       </c>
     </row>
     <row r="6" spans="1:31" ht="45.75">
-      <c r="A6" s="34">
+      <c r="A6" s="43">
         <v>134410</v>
       </c>
-      <c r="B6" s="35" t="s">
+      <c r="B6" s="44" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" s="45" t="s">
         <v>46</v>
       </c>
-      <c r="C6" s="40" t="s">
+      <c r="D6" s="43">
+        <v>261353</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" s="15" t="s">
         <v>47</v>
-      </c>
-      <c r="D6" s="34">
-        <v>261353</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="F6" s="15" t="s">
-        <v>48</v>
       </c>
       <c r="G6" s="12">
         <v>0</v>
@@ -1483,10 +1480,10 @@
         <v>120</v>
       </c>
       <c r="I6" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="J6" s="43" t="s">
         <v>49</v>
-      </c>
-      <c r="J6" s="34" t="s">
-        <v>50</v>
       </c>
       <c r="K6" s="10"/>
       <c r="L6" s="26" t="s">
@@ -1503,15 +1500,15 @@
       <c r="S6" s="33"/>
       <c r="T6" s="21"/>
       <c r="U6" s="33"/>
-      <c r="W6" s="34" t="s">
-        <v>29</v>
+      <c r="W6" s="43" t="s">
+        <v>27</v>
       </c>
       <c r="X6" s="10"/>
       <c r="Y6" s="10" t="s">
         <v>28</v>
       </c>
       <c r="Z6" s="10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AA6" s="21"/>
       <c r="AB6" s="10"/>
@@ -1520,15 +1517,15 @@
       <c r="AE6" s="10"/>
     </row>
     <row r="7" spans="1:31" ht="45.75">
-      <c r="A7" s="34"/>
-      <c r="B7" s="35"/>
-      <c r="C7" s="40"/>
-      <c r="D7" s="34"/>
+      <c r="A7" s="43"/>
+      <c r="B7" s="44"/>
+      <c r="C7" s="45"/>
+      <c r="D7" s="43"/>
       <c r="E7" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G7" s="12">
         <v>0</v>
@@ -1537,9 +1534,9 @@
         <v>500</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="J7" s="34"/>
+        <v>52</v>
+      </c>
+      <c r="J7" s="43"/>
       <c r="K7" s="10"/>
       <c r="L7" s="26" t="s">
         <v>27</v>
@@ -1555,13 +1552,13 @@
       <c r="S7" s="33"/>
       <c r="T7" s="21"/>
       <c r="U7" s="33"/>
-      <c r="W7" s="34"/>
+      <c r="W7" s="43"/>
       <c r="X7" s="10"/>
       <c r="Y7" s="10" t="s">
         <v>28</v>
       </c>
       <c r="Z7" s="10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AA7" s="21"/>
       <c r="AB7" s="10"/>
@@ -1570,15 +1567,15 @@
       <c r="AE7" s="12"/>
     </row>
     <row r="8" spans="1:31" ht="45.75">
-      <c r="A8" s="34"/>
-      <c r="B8" s="35"/>
-      <c r="C8" s="40"/>
-      <c r="D8" s="34"/>
+      <c r="A8" s="43"/>
+      <c r="B8" s="44"/>
+      <c r="C8" s="45"/>
+      <c r="D8" s="43"/>
       <c r="E8" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G8" s="12">
         <v>0</v>
@@ -1587,9 +1584,9 @@
         <v>30</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="J8" s="34"/>
+        <v>53</v>
+      </c>
+      <c r="J8" s="43"/>
       <c r="K8" s="10"/>
       <c r="L8" s="26" t="s">
         <v>27</v>
@@ -1605,42 +1602,42 @@
       <c r="S8" s="33"/>
       <c r="T8" s="21"/>
       <c r="U8" s="33"/>
-      <c r="W8" s="34"/>
+      <c r="W8" s="43"/>
       <c r="X8" s="10"/>
       <c r="Y8" s="10" t="s">
         <v>28</v>
       </c>
       <c r="Z8" s="10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AA8" s="21"/>
       <c r="AB8" s="10"/>
       <c r="AC8" s="10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AD8" s="10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AE8" s="12"/>
     </row>
     <row r="9" spans="1:31" ht="45.75">
-      <c r="A9" s="34">
+      <c r="A9" s="43">
         <v>142290</v>
       </c>
-      <c r="B9" s="35" t="s">
+      <c r="B9" s="44" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" s="45" t="s">
         <v>55</v>
       </c>
-      <c r="C9" s="40" t="s">
-        <v>56</v>
-      </c>
-      <c r="D9" s="34">
+      <c r="D9" s="43">
         <v>324000</v>
       </c>
       <c r="E9" s="12" t="s">
         <v>19</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G9" s="12">
         <v>0</v>
@@ -1649,10 +1646,10 @@
         <v>3</v>
       </c>
       <c r="I9" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="J9" s="43" t="s">
         <v>58</v>
-      </c>
-      <c r="J9" s="34" t="s">
-        <v>59</v>
       </c>
       <c r="K9" s="10"/>
       <c r="L9" s="26" t="s">
@@ -1663,52 +1660,52 @@
         <v>28</v>
       </c>
       <c r="O9" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P9" s="21"/>
       <c r="Q9" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="R9" s="21" t="s">
         <v>60</v>
-      </c>
-      <c r="R9" s="21" t="s">
-        <v>61</v>
       </c>
       <c r="S9" s="33"/>
       <c r="T9" s="21" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="U9" s="33"/>
-      <c r="W9" s="34" t="s">
-        <v>29</v>
+      <c r="W9" s="43" t="s">
+        <v>27</v>
       </c>
       <c r="X9" s="10"/>
       <c r="Y9" s="10" t="s">
         <v>28</v>
       </c>
       <c r="Z9" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA9" s="21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AB9" s="10"/>
       <c r="AC9" s="10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AD9" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AE9" s="12"/>
     </row>
     <row r="10" spans="1:31" ht="45.75">
-      <c r="A10" s="34"/>
-      <c r="B10" s="35"/>
-      <c r="C10" s="40"/>
-      <c r="D10" s="34"/>
+      <c r="A10" s="43"/>
+      <c r="B10" s="44"/>
+      <c r="C10" s="45"/>
+      <c r="D10" s="43"/>
       <c r="E10" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G10" s="12">
         <v>0</v>
@@ -1717,9 +1714,9 @@
         <v>400</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="J10" s="34"/>
+        <v>64</v>
+      </c>
+      <c r="J10" s="43"/>
       <c r="K10" s="10"/>
       <c r="L10" s="26" t="s">
         <v>27</v>
@@ -1735,34 +1732,34 @@
       <c r="S10" s="33"/>
       <c r="T10" s="21"/>
       <c r="U10" s="33"/>
-      <c r="W10" s="34"/>
+      <c r="W10" s="43"/>
       <c r="X10" s="10"/>
       <c r="Y10" s="10" t="s">
         <v>28</v>
       </c>
       <c r="Z10" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA10" s="21"/>
       <c r="AB10" s="10"/>
       <c r="AC10" s="10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AD10" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AE10" s="12"/>
     </row>
     <row r="11" spans="1:31" ht="45.75">
-      <c r="A11" s="34"/>
-      <c r="B11" s="35"/>
-      <c r="C11" s="40"/>
-      <c r="D11" s="34"/>
+      <c r="A11" s="43"/>
+      <c r="B11" s="44"/>
+      <c r="C11" s="45"/>
+      <c r="D11" s="43"/>
       <c r="E11" s="12" t="s">
         <v>19</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G11" s="12">
         <v>0</v>
@@ -1771,9 +1768,9 @@
         <v>3</v>
       </c>
       <c r="I11" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="J11" s="34"/>
+        <v>66</v>
+      </c>
+      <c r="J11" s="43"/>
       <c r="K11" s="10"/>
       <c r="L11" s="26" t="s">
         <v>27</v>
@@ -1783,58 +1780,58 @@
         <v>28</v>
       </c>
       <c r="O11" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P11" s="21"/>
       <c r="Q11" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="R11" s="21" t="s">
         <v>60</v>
-      </c>
-      <c r="R11" s="21" t="s">
-        <v>61</v>
       </c>
       <c r="S11" s="33"/>
       <c r="T11" s="21" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="U11" s="33"/>
-      <c r="W11" s="34"/>
+      <c r="W11" s="43"/>
       <c r="X11" s="23"/>
       <c r="Y11" s="10" t="s">
         <v>28</v>
       </c>
       <c r="Z11" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA11" s="21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AB11" s="10"/>
       <c r="AC11" s="10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AD11" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AE11" s="12"/>
     </row>
     <row r="12" spans="1:31" ht="45.75">
-      <c r="A12" s="34">
+      <c r="A12" s="43">
         <v>145829</v>
       </c>
-      <c r="B12" s="35" t="s">
+      <c r="B12" s="44" t="s">
+        <v>67</v>
+      </c>
+      <c r="C12" s="45" t="s">
         <v>68</v>
       </c>
-      <c r="C12" s="40" t="s">
+      <c r="D12" s="43">
+        <v>1151772</v>
+      </c>
+      <c r="E12" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="D12" s="34">
-        <v>1151772</v>
-      </c>
-      <c r="E12" s="12" t="s">
+      <c r="F12" s="12" t="s">
         <v>70</v>
-      </c>
-      <c r="F12" s="12" t="s">
-        <v>71</v>
       </c>
       <c r="G12" s="12">
         <v>0</v>
@@ -1843,9 +1840,9 @@
         <v>11500</v>
       </c>
       <c r="I12" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="J12" s="39" t="s">
+        <v>71</v>
+      </c>
+      <c r="J12" s="46" t="s">
         <v>26</v>
       </c>
       <c r="K12" s="10"/>
@@ -1863,15 +1860,15 @@
       <c r="S12" s="33"/>
       <c r="T12" s="21"/>
       <c r="U12" s="33"/>
-      <c r="W12" s="39" t="s">
-        <v>29</v>
+      <c r="W12" s="46" t="s">
+        <v>27</v>
       </c>
       <c r="X12" s="10"/>
       <c r="Y12" s="10" t="s">
         <v>28</v>
       </c>
       <c r="Z12" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA12" s="21"/>
       <c r="AB12" s="10"/>
@@ -1880,15 +1877,15 @@
       <c r="AE12" s="12"/>
     </row>
     <row r="13" spans="1:31" ht="45.75">
-      <c r="A13" s="34"/>
-      <c r="B13" s="35"/>
-      <c r="C13" s="40"/>
-      <c r="D13" s="34"/>
+      <c r="A13" s="43"/>
+      <c r="B13" s="44"/>
+      <c r="C13" s="45"/>
+      <c r="D13" s="43"/>
       <c r="E13" s="12" t="s">
         <v>19</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G13" s="12">
         <v>0</v>
@@ -1897,9 +1894,9 @@
         <v>1</v>
       </c>
       <c r="I13" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="J13" s="39"/>
+        <v>73</v>
+      </c>
+      <c r="J13" s="46"/>
       <c r="K13" s="10"/>
       <c r="L13" s="26" t="s">
         <v>27</v>
@@ -1909,58 +1906,58 @@
         <v>28</v>
       </c>
       <c r="O13" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P13" s="21"/>
       <c r="Q13" s="21" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="R13" s="21" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="S13" s="33"/>
       <c r="T13" s="21" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="U13" s="33"/>
-      <c r="W13" s="39"/>
+      <c r="W13" s="46"/>
       <c r="X13" s="10"/>
       <c r="Y13" s="10" t="s">
         <v>28</v>
       </c>
       <c r="Z13" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA13" s="21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AB13" s="10"/>
       <c r="AC13" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AD13" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="AE13" s="12"/>
+    </row>
+    <row r="14" spans="1:31" ht="45.75">
+      <c r="A14" s="43">
+        <v>100344</v>
+      </c>
+      <c r="B14" s="44" t="s">
         <v>75</v>
       </c>
-      <c r="AE13" s="12"/>
-    </row>
-    <row r="14" spans="1:31" ht="45.75">
-      <c r="A14" s="34">
-        <v>100344</v>
-      </c>
-      <c r="B14" s="35" t="s">
+      <c r="C14" s="49" t="s">
         <v>76</v>
       </c>
-      <c r="C14" s="36" t="s">
+      <c r="D14" s="51">
+        <v>996991</v>
+      </c>
+      <c r="E14" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="D14" s="37">
-        <v>996991</v>
-      </c>
-      <c r="E14" s="15" t="s">
+      <c r="F14" s="15" t="s">
         <v>78</v>
-      </c>
-      <c r="F14" s="15" t="s">
-        <v>79</v>
       </c>
       <c r="G14" s="15">
         <v>270</v>
@@ -1969,8 +1966,8 @@
         <v>50000</v>
       </c>
       <c r="I14" s="15"/>
-      <c r="J14" s="41" t="s">
-        <v>80</v>
+      <c r="J14" s="47" t="s">
+        <v>79</v>
       </c>
       <c r="K14" s="10"/>
       <c r="L14" s="26" t="s">
@@ -1978,7 +1975,7 @@
       </c>
       <c r="M14" s="21"/>
       <c r="N14" s="32" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O14" s="21"/>
       <c r="P14" s="21"/>
@@ -1987,15 +1984,15 @@
       <c r="S14" s="33"/>
       <c r="T14" s="21"/>
       <c r="U14" s="33"/>
-      <c r="W14" s="39" t="s">
-        <v>29</v>
+      <c r="W14" s="46" t="s">
+        <v>27</v>
       </c>
       <c r="X14" s="10"/>
       <c r="Y14" s="10" t="s">
         <v>28</v>
       </c>
       <c r="Z14" s="10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AA14" s="21"/>
       <c r="AB14" s="10"/>
@@ -2004,15 +2001,15 @@
       <c r="AE14" s="15"/>
     </row>
     <row r="15" spans="1:31" ht="45.75">
-      <c r="A15" s="34"/>
-      <c r="B15" s="35"/>
-      <c r="C15" s="36"/>
-      <c r="D15" s="38"/>
+      <c r="A15" s="43"/>
+      <c r="B15" s="44"/>
+      <c r="C15" s="49"/>
+      <c r="D15" s="52"/>
       <c r="E15" s="15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F15" s="15" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G15" s="15">
         <v>0</v>
@@ -2021,16 +2018,16 @@
         <v>80000</v>
       </c>
       <c r="I15" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="J15" s="42"/>
+        <v>82</v>
+      </c>
+      <c r="J15" s="54"/>
       <c r="K15" s="10"/>
       <c r="L15" s="26" t="s">
         <v>27</v>
       </c>
       <c r="M15" s="21"/>
       <c r="N15" s="32" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O15" s="21"/>
       <c r="P15" s="21"/>
@@ -2039,13 +2036,13 @@
       <c r="S15" s="33"/>
       <c r="T15" s="21"/>
       <c r="U15" s="33"/>
-      <c r="W15" s="39"/>
+      <c r="W15" s="46"/>
       <c r="X15" s="10"/>
       <c r="Y15" s="10" t="s">
         <v>28</v>
       </c>
       <c r="Z15" s="10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AA15" s="21"/>
       <c r="AB15" s="10"/>
@@ -2054,15 +2051,15 @@
       <c r="AE15" s="15"/>
     </row>
     <row r="16" spans="1:31" ht="45.75">
-      <c r="A16" s="41"/>
-      <c r="B16" s="49"/>
+      <c r="A16" s="47"/>
+      <c r="B16" s="48"/>
       <c r="C16" s="50"/>
-      <c r="D16" s="51"/>
-      <c r="E16" s="52" t="s">
+      <c r="D16" s="53"/>
+      <c r="E16" s="36" t="s">
+        <v>83</v>
+      </c>
+      <c r="F16" s="15" t="s">
         <v>84</v>
-      </c>
-      <c r="F16" s="15" t="s">
-        <v>85</v>
       </c>
       <c r="G16" s="15">
         <v>0</v>
@@ -2071,14 +2068,14 @@
         <v>60</v>
       </c>
       <c r="I16" s="15"/>
-      <c r="J16" s="43"/>
+      <c r="J16" s="55"/>
       <c r="K16" s="10"/>
       <c r="L16" s="26" t="s">
         <v>27</v>
       </c>
       <c r="M16" s="21"/>
       <c r="N16" s="32" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O16" s="21"/>
       <c r="P16" s="21"/>
@@ -2093,7 +2090,7 @@
         <v>28</v>
       </c>
       <c r="Z16" s="10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AA16" s="21"/>
       <c r="AB16" s="10"/>
@@ -2101,24 +2098,24 @@
       <c r="AD16" s="10"/>
       <c r="AE16" s="15"/>
     </row>
-    <row r="17" spans="1:10" ht="45.75">
-      <c r="A17" s="55">
+    <row r="17" spans="1:12" ht="45.75">
+      <c r="A17" s="39">
         <v>144399</v>
       </c>
-      <c r="B17" s="56" t="s">
+      <c r="B17" s="40" t="s">
+        <v>85</v>
+      </c>
+      <c r="C17" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="C17" s="57" t="s">
-        <v>87</v>
-      </c>
-      <c r="D17" s="58">
+      <c r="D17" s="42">
         <v>43615</v>
       </c>
-      <c r="E17" s="55" t="s">
+      <c r="E17" s="39" t="s">
+        <v>77</v>
+      </c>
+      <c r="F17" s="35" t="s">
         <v>78</v>
-      </c>
-      <c r="F17" s="48" t="s">
-        <v>79</v>
       </c>
       <c r="G17">
         <v>270</v>
@@ -2126,28 +2123,31 @@
       <c r="H17">
         <v>302</v>
       </c>
-      <c r="J17" s="53" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="30.75">
+      <c r="J17" s="37" t="s">
+        <v>87</v>
+      </c>
+      <c r="L17" s="26" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="30.75">
       <c r="A18" s="10">
         <v>1000353</v>
       </c>
-      <c r="B18" s="54" t="s">
+      <c r="B18" s="38" t="s">
+        <v>88</v>
+      </c>
+      <c r="C18" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="C18" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="D18" s="47">
+      <c r="D18" s="34">
         <v>24533</v>
       </c>
       <c r="E18" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="F18" s="35" t="s">
         <v>78</v>
-      </c>
-      <c r="F18" s="48" t="s">
-        <v>79</v>
       </c>
       <c r="G18">
         <v>270</v>
@@ -2156,11 +2156,32 @@
         <v>288</v>
       </c>
       <c r="J18" t="s">
-        <v>80</v>
+        <v>79</v>
+      </c>
+      <c r="L18" s="26" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="D14:D16"/>
+    <mergeCell ref="W14:W15"/>
+    <mergeCell ref="J14:J16"/>
+    <mergeCell ref="W12:W13"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="D9:D11"/>
+    <mergeCell ref="J9:J11"/>
+    <mergeCell ref="W9:W11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="J12:J13"/>
     <mergeCell ref="W6:W8"/>
     <mergeCell ref="A3:A5"/>
     <mergeCell ref="B3:B5"/>
@@ -2173,24 +2194,6 @@
     <mergeCell ref="C6:C8"/>
     <mergeCell ref="D6:D8"/>
     <mergeCell ref="J6:J8"/>
-    <mergeCell ref="W12:W13"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:B11"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="D9:D11"/>
-    <mergeCell ref="J9:J11"/>
-    <mergeCell ref="W9:W11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="J12:J13"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="C14:C16"/>
-    <mergeCell ref="D14:D16"/>
-    <mergeCell ref="W14:W15"/>
-    <mergeCell ref="J14:J16"/>
   </mergeCells>
   <dataValidations count="12">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD2:AD16" xr:uid="{2656783B-E017-4B69-B2BF-55ABED0028FD}">
@@ -2220,7 +2223,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T16" xr:uid="{49AA078C-7503-4232-B72A-DDCE16B958A0}">
       <formula1>"National, Regional, City, Community"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L16" xr:uid="{49308E06-A525-4002-A359-4264ED98CF3B}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L18" xr:uid="{49308E06-A525-4002-A359-4264ED98CF3B}">
       <formula1>"Non-VF, VF"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R16" xr:uid="{36179383-640F-4883-9622-D7681396F9AA}">
@@ -2304,7 +2307,7 @@
         <v>7</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J1" s="9" t="s">
         <v>8</v>
@@ -2316,10 +2319,10 @@
         <v>10</v>
       </c>
       <c r="M1" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="N1" s="8" t="s">
         <v>92</v>
-      </c>
-      <c r="N1" s="8" t="s">
-        <v>93</v>
       </c>
       <c r="O1" s="7" t="s">
         <v>13</v>
@@ -2371,34 +2374,34 @@
       </c>
       <c r="L2" s="10"/>
       <c r="M2" s="10" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="N2" s="10"/>
       <c r="O2" t="s">
         <v>28</v>
       </c>
       <c r="P2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19">
+      <c r="A3" s="43">
+        <v>119366</v>
+      </c>
+      <c r="B3" s="43" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="3" spans="1:19">
-      <c r="A3" s="34">
-        <v>119366</v>
-      </c>
-      <c r="B3" s="34" t="s">
+      <c r="C3" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="40" t="s">
-        <v>32</v>
-      </c>
-      <c r="D3" s="34">
+      <c r="D3" s="43">
         <v>1007201</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G3" s="12">
         <v>0</v>
@@ -2408,33 +2411,33 @@
       </c>
       <c r="I3" s="12"/>
       <c r="J3" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="K3" s="41" t="s">
-        <v>95</v>
+        <v>34</v>
+      </c>
+      <c r="K3" s="47" t="s">
+        <v>94</v>
       </c>
       <c r="L3" s="10"/>
-      <c r="M3" s="41" t="s">
-        <v>29</v>
+      <c r="M3" s="47" t="s">
+        <v>27</v>
       </c>
       <c r="N3" s="10"/>
       <c r="O3" t="s">
         <v>28</v>
       </c>
       <c r="P3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:19">
-      <c r="A4" s="34"/>
-      <c r="B4" s="34"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="34"/>
+      <c r="A4" s="43"/>
+      <c r="B4" s="43"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="43"/>
       <c r="E4" s="12" t="s">
         <v>19</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G4" s="12">
         <v>0</v>
@@ -2444,33 +2447,33 @@
       </c>
       <c r="I4" s="12"/>
       <c r="J4" s="12"/>
-      <c r="K4" s="42"/>
+      <c r="K4" s="54"/>
       <c r="L4" s="10"/>
-      <c r="M4" s="42"/>
+      <c r="M4" s="54"/>
       <c r="N4" s="10"/>
       <c r="O4" t="s">
         <v>28</v>
       </c>
       <c r="P4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="R4" t="s">
+        <v>37</v>
+      </c>
+      <c r="S4" t="s">
         <v>38</v>
       </c>
-      <c r="S4" t="s">
-        <v>39</v>
-      </c>
     </row>
     <row r="5" spans="1:19">
-      <c r="A5" s="34"/>
-      <c r="B5" s="34"/>
-      <c r="C5" s="40"/>
-      <c r="D5" s="34"/>
+      <c r="A5" s="43"/>
+      <c r="B5" s="43"/>
+      <c r="C5" s="45"/>
+      <c r="D5" s="43"/>
       <c r="E5" s="12" t="s">
         <v>19</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G5" s="12">
         <v>0</v>
@@ -2482,43 +2485,43 @@
         <v>1200000</v>
       </c>
       <c r="J5" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="K5" s="43"/>
+        <v>95</v>
+      </c>
+      <c r="K5" s="55"/>
       <c r="L5" s="10"/>
-      <c r="M5" s="43"/>
+      <c r="M5" s="55"/>
       <c r="N5" s="10"/>
       <c r="O5" t="s">
         <v>28</v>
       </c>
       <c r="P5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="R5" t="s">
+        <v>44</v>
+      </c>
+      <c r="S5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19">
+      <c r="A6" s="43">
+        <v>134410</v>
+      </c>
+      <c r="B6" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="S5" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19">
-      <c r="A6" s="34">
-        <v>134410</v>
-      </c>
-      <c r="B6" s="34" t="s">
+      <c r="C6" s="45" t="s">
         <v>46</v>
       </c>
-      <c r="C6" s="40" t="s">
+      <c r="D6" s="43">
+        <v>261353</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="F6" s="15" t="s">
         <v>47</v>
-      </c>
-      <c r="D6" s="34">
-        <v>261353</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="F6" s="15" t="s">
-        <v>48</v>
       </c>
       <c r="G6" s="12">
         <v>0</v>
@@ -2527,33 +2530,33 @@
         <v>120</v>
       </c>
       <c r="J6" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="K6" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="K6" s="41" t="s">
-        <v>50</v>
-      </c>
       <c r="L6" s="10"/>
-      <c r="M6" s="41" t="s">
-        <v>29</v>
+      <c r="M6" s="47" t="s">
+        <v>27</v>
       </c>
       <c r="N6" s="10"/>
       <c r="O6" t="s">
         <v>28</v>
       </c>
       <c r="P6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19">
+      <c r="A7" s="43"/>
+      <c r="B7" s="43"/>
+      <c r="C7" s="45"/>
+      <c r="D7" s="43"/>
+      <c r="E7" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="F7" s="15" t="s">
         <v>51</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19">
-      <c r="A7" s="34"/>
-      <c r="B7" s="34"/>
-      <c r="C7" s="40"/>
-      <c r="D7" s="34"/>
-      <c r="E7" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="F7" s="15" t="s">
-        <v>52</v>
       </c>
       <c r="G7" s="12">
         <v>0</v>
@@ -2563,29 +2566,29 @@
       </c>
       <c r="I7" s="12"/>
       <c r="J7" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="K7" s="42"/>
+        <v>52</v>
+      </c>
+      <c r="K7" s="54"/>
       <c r="L7" s="10"/>
-      <c r="M7" s="42"/>
+      <c r="M7" s="54"/>
       <c r="N7" s="10"/>
       <c r="O7" t="s">
         <v>28</v>
       </c>
       <c r="P7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:19">
-      <c r="A8" s="34"/>
-      <c r="B8" s="34"/>
-      <c r="C8" s="40"/>
-      <c r="D8" s="34"/>
+      <c r="A8" s="43"/>
+      <c r="B8" s="43"/>
+      <c r="C8" s="45"/>
+      <c r="D8" s="43"/>
       <c r="E8" s="12" t="s">
         <v>19</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G8" s="12">
         <v>0</v>
@@ -2595,43 +2598,43 @@
       </c>
       <c r="I8" s="12"/>
       <c r="J8" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="K8" s="43"/>
+        <v>53</v>
+      </c>
+      <c r="K8" s="55"/>
       <c r="L8" s="10"/>
-      <c r="M8" s="43"/>
+      <c r="M8" s="55"/>
       <c r="N8" s="10"/>
       <c r="O8" t="s">
         <v>28</v>
       </c>
       <c r="P8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="R8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:19" ht="30.75">
-      <c r="A9" s="34">
+      <c r="A9" s="43">
         <v>142290</v>
       </c>
-      <c r="B9" s="34" t="s">
+      <c r="B9" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" s="45" t="s">
         <v>55</v>
       </c>
-      <c r="C9" s="40" t="s">
-        <v>56</v>
-      </c>
-      <c r="D9" s="34">
+      <c r="D9" s="43">
         <v>324000</v>
       </c>
       <c r="E9" s="12" t="s">
         <v>19</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G9" s="12">
         <v>0</v>
@@ -2641,39 +2644,39 @@
       </c>
       <c r="I9" s="12"/>
       <c r="J9" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="K9" s="47" t="s">
         <v>58</v>
       </c>
-      <c r="K9" s="41" t="s">
-        <v>59</v>
-      </c>
       <c r="L9" s="10"/>
-      <c r="M9" s="41" t="s">
-        <v>29</v>
+      <c r="M9" s="47" t="s">
+        <v>27</v>
       </c>
       <c r="N9" s="10"/>
       <c r="O9" t="s">
         <v>28</v>
       </c>
       <c r="P9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="R9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:19">
-      <c r="A10" s="34"/>
-      <c r="B10" s="34"/>
-      <c r="C10" s="40"/>
-      <c r="D10" s="34"/>
+      <c r="A10" s="43"/>
+      <c r="B10" s="43"/>
+      <c r="C10" s="45"/>
+      <c r="D10" s="43"/>
       <c r="E10" s="12" t="s">
         <v>19</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G10" s="12">
         <v>0</v>
@@ -2683,35 +2686,35 @@
       </c>
       <c r="I10" s="12"/>
       <c r="J10" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="K10" s="42"/>
+        <v>64</v>
+      </c>
+      <c r="K10" s="54"/>
       <c r="L10" s="10"/>
-      <c r="M10" s="42"/>
+      <c r="M10" s="54"/>
       <c r="N10" s="10"/>
       <c r="O10" t="s">
         <v>28</v>
       </c>
       <c r="P10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="R10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:19">
-      <c r="A11" s="34"/>
-      <c r="B11" s="34"/>
-      <c r="C11" s="40"/>
-      <c r="D11" s="34"/>
+      <c r="A11" s="43"/>
+      <c r="B11" s="43"/>
+      <c r="C11" s="45"/>
+      <c r="D11" s="43"/>
       <c r="E11" s="12" t="s">
         <v>19</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G11" s="12">
         <v>0</v>
@@ -2721,43 +2724,43 @@
       </c>
       <c r="I11" s="12"/>
       <c r="J11" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="K11" s="43"/>
+        <v>66</v>
+      </c>
+      <c r="K11" s="55"/>
       <c r="L11" s="10"/>
-      <c r="M11" s="43"/>
+      <c r="M11" s="55"/>
       <c r="N11" s="20"/>
       <c r="O11" t="s">
         <v>28</v>
       </c>
       <c r="P11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="R11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:19" ht="17.25" customHeight="1">
-      <c r="A12" s="34">
+      <c r="A12" s="43">
         <v>145829</v>
       </c>
-      <c r="B12" s="34" t="s">
+      <c r="B12" s="43" t="s">
+        <v>67</v>
+      </c>
+      <c r="C12" s="45" t="s">
         <v>68</v>
       </c>
-      <c r="C12" s="40" t="s">
-        <v>69</v>
-      </c>
-      <c r="D12" s="34">
+      <c r="D12" s="43">
         <v>1151772</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G12" s="12">
         <v>0</v>
@@ -2767,33 +2770,33 @@
       </c>
       <c r="I12" s="18"/>
       <c r="J12" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="K12" s="44" t="s">
+        <v>71</v>
+      </c>
+      <c r="K12" s="56" t="s">
         <v>26</v>
       </c>
       <c r="L12" s="10"/>
-      <c r="M12" s="44" t="s">
-        <v>29</v>
+      <c r="M12" s="56" t="s">
+        <v>27</v>
       </c>
       <c r="N12" s="10"/>
       <c r="O12" t="s">
         <v>28</v>
       </c>
       <c r="P12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A13" s="34"/>
-      <c r="B13" s="34"/>
-      <c r="C13" s="40"/>
-      <c r="D13" s="34"/>
+      <c r="A13" s="43"/>
+      <c r="B13" s="43"/>
+      <c r="C13" s="45"/>
+      <c r="D13" s="43"/>
       <c r="E13" s="12" t="s">
         <v>19</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G13" s="12">
         <v>0</v>
@@ -2803,39 +2806,39 @@
       </c>
       <c r="I13" s="17"/>
       <c r="J13" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="K13" s="45"/>
+        <v>73</v>
+      </c>
+      <c r="K13" s="57"/>
       <c r="L13" s="10"/>
-      <c r="M13" s="45"/>
+      <c r="M13" s="57"/>
       <c r="N13" s="10"/>
       <c r="O13" t="s">
         <v>28</v>
       </c>
       <c r="P13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="R13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S13" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19">
+      <c r="A14" s="43">
+        <v>100344</v>
+      </c>
+      <c r="B14" s="43" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="14" spans="1:19">
-      <c r="A14" s="34">
-        <v>100344</v>
-      </c>
-      <c r="B14" s="34" t="s">
-        <v>76</v>
-      </c>
-      <c r="C14" s="44"/>
-      <c r="D14" s="44"/>
+      <c r="C14" s="56"/>
+      <c r="D14" s="56"/>
       <c r="E14" s="15" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G14" s="15">
         <v>270</v>
@@ -2847,27 +2850,27 @@
       <c r="J14" s="19"/>
       <c r="K14" s="10"/>
       <c r="L14" s="10"/>
-      <c r="M14" s="44" t="s">
-        <v>29</v>
+      <c r="M14" s="56" t="s">
+        <v>27</v>
       </c>
       <c r="N14" s="10"/>
       <c r="O14" t="s">
         <v>28</v>
       </c>
       <c r="P14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:19">
-      <c r="A15" s="34"/>
-      <c r="B15" s="34"/>
-      <c r="C15" s="46"/>
-      <c r="D15" s="46"/>
+      <c r="A15" s="43"/>
+      <c r="B15" s="43"/>
+      <c r="C15" s="58"/>
+      <c r="D15" s="58"/>
       <c r="E15" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F15" s="15" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G15" s="15">
         <v>0</v>
@@ -2877,29 +2880,29 @@
       </c>
       <c r="I15" s="15"/>
       <c r="J15" s="15" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K15" s="10"/>
       <c r="L15" s="10"/>
-      <c r="M15" s="45"/>
+      <c r="M15" s="57"/>
       <c r="N15" s="10"/>
       <c r="O15" t="s">
         <v>28</v>
       </c>
       <c r="P15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:19">
-      <c r="A16" s="34"/>
-      <c r="B16" s="34"/>
-      <c r="C16" s="45"/>
-      <c r="D16" s="45"/>
+      <c r="A16" s="43"/>
+      <c r="B16" s="43"/>
+      <c r="C16" s="57"/>
+      <c r="D16" s="57"/>
       <c r="E16" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="F16" s="15" t="s">
         <v>84</v>
-      </c>
-      <c r="F16" s="15" t="s">
-        <v>85</v>
       </c>
       <c r="G16" s="15">
         <v>0</v>
@@ -2917,24 +2920,19 @@
         <v>28</v>
       </c>
       <c r="P16" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="K12:K13"/>
-    <mergeCell ref="M12:M13"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="C14:C16"/>
-    <mergeCell ref="D14:D16"/>
-    <mergeCell ref="M14:M15"/>
-    <mergeCell ref="K3:K5"/>
-    <mergeCell ref="M3:M5"/>
-    <mergeCell ref="K6:K8"/>
-    <mergeCell ref="M6:M8"/>
-    <mergeCell ref="K9:K11"/>
-    <mergeCell ref="M9:M11"/>
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="B3:B5"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="A6:A8"/>
+    <mergeCell ref="B6:B8"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="B9:B11"/>
     <mergeCell ref="C9:C11"/>
@@ -2943,14 +2941,19 @@
     <mergeCell ref="B12:B13"/>
     <mergeCell ref="C12:C13"/>
     <mergeCell ref="D12:D13"/>
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="B3:B5"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="A6:A8"/>
-    <mergeCell ref="B6:B8"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="K3:K5"/>
+    <mergeCell ref="M3:M5"/>
+    <mergeCell ref="K6:K8"/>
+    <mergeCell ref="M6:M8"/>
+    <mergeCell ref="K9:K11"/>
+    <mergeCell ref="M9:M11"/>
+    <mergeCell ref="K12:K13"/>
+    <mergeCell ref="M12:M13"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="D14:D16"/>
+    <mergeCell ref="M14:M15"/>
   </mergeCells>
   <dataValidations count="6">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E12" xr:uid="{8A6EECDF-213D-4435-9AB2-44F0897711E3}"/>
@@ -3053,7 +3056,7 @@
         <v>869916</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>24</v>
@@ -3073,19 +3076,19 @@
         <v>119366</v>
       </c>
       <c r="B3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="D3">
         <v>1007201</v>
       </c>
       <c r="E3" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>98</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>99</v>
       </c>
       <c r="G3" s="3">
         <v>0</v>
@@ -3094,7 +3097,7 @@
         <v>12</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -3102,19 +3105,19 @@
         <v>119366</v>
       </c>
       <c r="B4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="D4">
         <v>1007201</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G4" s="3">
         <v>0</v>
@@ -3129,10 +3132,10 @@
         <v>119366</v>
       </c>
       <c r="B5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="D5">
         <v>1007201</v>
@@ -3141,7 +3144,7 @@
         <v>19</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G5" s="3">
         <v>0</v>
@@ -3150,7 +3153,7 @@
         <v>5</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -3158,19 +3161,19 @@
         <v>134410</v>
       </c>
       <c r="B6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>47</v>
       </c>
       <c r="D6">
         <v>261353</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G6" s="3">
         <v>0</v>
@@ -3179,7 +3182,7 @@
         <v>6</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -3187,19 +3190,19 @@
         <v>134410</v>
       </c>
       <c r="B7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>47</v>
       </c>
       <c r="D7">
         <v>261353</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G7" s="3">
         <v>0</v>
@@ -3208,7 +3211,7 @@
         <v>10</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -3216,19 +3219,19 @@
         <v>134410</v>
       </c>
       <c r="B8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>47</v>
       </c>
       <c r="D8">
         <v>261353</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G8" s="3">
         <v>0</v>
@@ -3237,7 +3240,7 @@
         <v>5</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -3245,10 +3248,10 @@
         <v>142290</v>
       </c>
       <c r="B9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>56</v>
       </c>
       <c r="D9">
         <v>324000</v>
@@ -3257,7 +3260,7 @@
         <v>19</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G9" s="3">
         <v>0</v>
@@ -3266,7 +3269,7 @@
         <v>3</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -3274,19 +3277,19 @@
         <v>142290</v>
       </c>
       <c r="B10" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>56</v>
       </c>
       <c r="D10">
         <v>324000</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G10" s="3">
         <v>0</v>
@@ -3295,7 +3298,7 @@
         <v>6</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -3303,19 +3306,19 @@
         <v>142290</v>
       </c>
       <c r="B11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>56</v>
       </c>
       <c r="D11">
         <v>324000</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G11" s="3">
         <v>0</v>
@@ -3324,7 +3327,7 @@
         <v>3</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="17.25" customHeight="1">
@@ -3332,19 +3335,19 @@
         <v>145829</v>
       </c>
       <c r="B12" t="s">
+        <v>67</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>68</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>69</v>
       </c>
       <c r="D12">
         <v>1151772</v>
       </c>
       <c r="E12" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>106</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>107</v>
       </c>
       <c r="G12" s="3">
         <v>0</v>
@@ -3353,7 +3356,7 @@
         <v>208</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="15.75" customHeight="1">
@@ -3361,10 +3364,10 @@
         <v>145829</v>
       </c>
       <c r="B13" t="s">
+        <v>67</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>68</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>69</v>
       </c>
       <c r="D13">
         <v>1151772</v>
@@ -3373,7 +3376,7 @@
         <v>19</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G13" s="3">
         <v>0</v>
@@ -3382,7 +3385,7 @@
         <v>1</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -3390,13 +3393,13 @@
         <v>1000344</v>
       </c>
       <c r="B14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G14" s="4">
         <v>270</v>
@@ -3411,13 +3414,13 @@
         <v>1000344</v>
       </c>
       <c r="B15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G15" s="4">
         <v>0</v>
@@ -3426,7 +3429,7 @@
         <v>200</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -3434,13 +3437,13 @@
         <v>1000344</v>
       </c>
       <c r="B16" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G16" s="4">
         <v>0</v>
@@ -3499,106 +3502,106 @@
     </row>
     <row r="2" spans="1:2" ht="45.75">
       <c r="A2" s="59" t="s">
+        <v>109</v>
+      </c>
+      <c r="B2" s="28" t="s">
         <v>110</v>
-      </c>
-      <c r="B2" s="28" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="59" t="s">
+        <v>111</v>
+      </c>
+      <c r="B3" s="28" t="s">
         <v>112</v>
-      </c>
-      <c r="B3" s="28" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="30.75">
       <c r="A4" s="59" t="s">
+        <v>113</v>
+      </c>
+      <c r="B4" s="28" t="s">
         <v>114</v>
-      </c>
-      <c r="B4" s="28" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="30.75">
       <c r="A5" s="59" t="s">
+        <v>115</v>
+      </c>
+      <c r="B5" s="28" t="s">
         <v>116</v>
-      </c>
-      <c r="B5" s="28" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="91.5">
       <c r="A6" s="59" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B6" s="28" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="45.75">
       <c r="A7" s="59" t="s">
+        <v>118</v>
+      </c>
+      <c r="B7" s="28" t="s">
         <v>119</v>
-      </c>
-      <c r="B7" s="28" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="45.75">
       <c r="A8" s="59" t="s">
+        <v>120</v>
+      </c>
+      <c r="B8" s="28" t="s">
         <v>121</v>
-      </c>
-      <c r="B8" s="28" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="45.75">
       <c r="A9" s="59" t="s">
+        <v>122</v>
+      </c>
+      <c r="B9" s="28" t="s">
         <v>123</v>
-      </c>
-      <c r="B9" s="28" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="30.75">
       <c r="A10" s="59" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B10" s="60" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="30.75">
       <c r="A11" s="59" t="s">
+        <v>125</v>
+      </c>
+      <c r="B11" s="60" t="s">
         <v>126</v>
-      </c>
-      <c r="B11" s="60" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="45.75">
       <c r="A12" s="59" t="s">
+        <v>127</v>
+      </c>
+      <c r="B12" s="28" t="s">
         <v>128</v>
-      </c>
-      <c r="B12" s="28" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="30.75">
       <c r="A13" s="59" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B13" s="60" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="59" t="s">
+        <v>130</v>
+      </c>
+      <c r="B14" s="60" t="s">
         <v>131</v>
-      </c>
-      <c r="B14" s="60" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="30.75">
@@ -3606,47 +3609,47 @@
         <v>23</v>
       </c>
       <c r="B15" s="60" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="30.75">
       <c r="A16" s="59" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B16" s="60" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30.75">
       <c r="A17" s="59" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B17" s="28" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="30.75">
       <c r="A18" s="59" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B18" s="60" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="76.5">
       <c r="A19" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="B19" s="60" t="s">
         <v>137</v>
-      </c>
-      <c r="B19" s="60" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="30.75">
       <c r="A20" s="59" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B20" s="60" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="45.75">
@@ -3654,15 +3657,15 @@
         <v>19</v>
       </c>
       <c r="B21" s="61" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="30.75">
       <c r="A22" s="59" t="s">
+        <v>140</v>
+      </c>
+      <c r="B22" s="60" t="s">
         <v>141</v>
-      </c>
-      <c r="B22" s="60" t="s">
-        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -3671,8 +3674,65 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0d2b1cfbe0bead55dc04bff20486709a">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3ed273af6605fa6a207dd3965c2d078" ns2:_="" ns3:_="">
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
+    <SharedWithUsers xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59">
+      <UserInfo>
+        <DisplayName>Suranga Karavita</DisplayName>
+        <AccountId>1730</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Hakshala David</DisplayName>
+        <AccountId>2305</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Afraa Mohamed</DisplayName>
+        <AccountId>2365</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Benjamin Keller</DisplayName>
+        <AccountId>1227</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Riad Meddeb</DisplayName>
+        <AccountId>9</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Stefano Pistolese</DisplayName>
+        <AccountId>772</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Pabasara Herath</DisplayName>
+        <AccountId>2367</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="dd25160c21e587dbb66203dfb8c7aa52">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="05ccd5be12d50c438f9536854e894bcb" ns2:_="" ns3:_="">
     <xsd:import namespace="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
     <xsd:import namespace="fb9e4d32-074f-4c04-81ef-e811753dfd59"/>
     <xsd:element name="properties">
@@ -3697,6 +3757,7 @@
                 <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
                 <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -3776,6 +3837,11 @@
     <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -3919,65 +3985,8 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
-    <SharedWithUsers xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59">
-      <UserInfo>
-        <DisplayName>Suranga Karavita</DisplayName>
-        <AccountId>1730</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Hakshala David</DisplayName>
-        <AccountId>2305</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Afraa Mohamed</DisplayName>
-        <AccountId>2365</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Benjamin Keller</DisplayName>
-        <AccountId>1227</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Riad Meddeb</DisplayName>
-        <AccountId>9</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Stefano Pistolese</DisplayName>
-        <AccountId>772</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Pabasara Herath</DisplayName>
-        <AccountId>2367</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD35035E-53EF-4346-8B10-4ECA462E02DA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{60C138E8-386B-4289-AC99-AD84197522D7}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3985,5 +3994,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{60C138E8-386B-4289-AC99-AD84197522D7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B375FF7C-6204-4D0D-9323-0CEED1C8EC77}"/>
 </file>
--- a/01_Input/00_CO Validation/Sri Lanka - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Sri Lanka - Energy Projects.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27504"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28224"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="426" documentId="11_59392953A5B08644DD0FF8ADE13F31B695A83B27" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B94C4284-A51B-486B-9BCA-CB86E1466A18}"/>
+  <xr:revisionPtr revIDLastSave="428" documentId="11_59392953A5B08644DD0FF8ADE13F31B695A83B27" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B4D8BA4-0AEF-4345-B64D-5A991E2D2F6B}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projects (3)" sheetId="4" r:id="rId1"/>
-    <sheet name="Projects (2)" sheetId="3" r:id="rId2"/>
-    <sheet name="Projects" sheetId="1" r:id="rId3"/>
+    <sheet name="Projects (2)" sheetId="3" state="hidden" r:id="rId2"/>
+    <sheet name="Projects" sheetId="1" state="hidden" r:id="rId3"/>
     <sheet name="Beneficiary Categories" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191028"/>
@@ -766,16 +766,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
@@ -796,10 +790,16 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1276,10 +1276,10 @@
       <c r="A3" s="43">
         <v>119366</v>
       </c>
-      <c r="B3" s="44" t="s">
+      <c r="B3" s="45" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="45" t="s">
+      <c r="C3" s="55" t="s">
         <v>31</v>
       </c>
       <c r="D3" s="43">
@@ -1336,8 +1336,8 @@
     </row>
     <row r="4" spans="1:31" ht="45.75">
       <c r="A4" s="43"/>
-      <c r="B4" s="44"/>
-      <c r="C4" s="45"/>
+      <c r="B4" s="45"/>
+      <c r="C4" s="55"/>
       <c r="D4" s="43"/>
       <c r="E4" s="12" t="s">
         <v>32</v>
@@ -1388,8 +1388,8 @@
     </row>
     <row r="5" spans="1:31" ht="45.75">
       <c r="A5" s="43"/>
-      <c r="B5" s="44"/>
-      <c r="C5" s="45"/>
+      <c r="B5" s="45"/>
+      <c r="C5" s="55"/>
       <c r="D5" s="43"/>
       <c r="E5" s="12" t="s">
         <v>19</v>
@@ -1458,10 +1458,10 @@
       <c r="A6" s="43">
         <v>134410</v>
       </c>
-      <c r="B6" s="44" t="s">
+      <c r="B6" s="45" t="s">
         <v>45</v>
       </c>
-      <c r="C6" s="45" t="s">
+      <c r="C6" s="55" t="s">
         <v>46</v>
       </c>
       <c r="D6" s="43">
@@ -1518,8 +1518,8 @@
     </row>
     <row r="7" spans="1:31" ht="45.75">
       <c r="A7" s="43"/>
-      <c r="B7" s="44"/>
-      <c r="C7" s="45"/>
+      <c r="B7" s="45"/>
+      <c r="C7" s="55"/>
       <c r="D7" s="43"/>
       <c r="E7" s="12" t="s">
         <v>32</v>
@@ -1568,8 +1568,8 @@
     </row>
     <row r="8" spans="1:31" ht="45.75">
       <c r="A8" s="43"/>
-      <c r="B8" s="44"/>
-      <c r="C8" s="45"/>
+      <c r="B8" s="45"/>
+      <c r="C8" s="55"/>
       <c r="D8" s="43"/>
       <c r="E8" s="12" t="s">
         <v>32</v>
@@ -1624,10 +1624,10 @@
       <c r="A9" s="43">
         <v>142290</v>
       </c>
-      <c r="B9" s="44" t="s">
+      <c r="B9" s="45" t="s">
         <v>54</v>
       </c>
-      <c r="C9" s="45" t="s">
+      <c r="C9" s="55" t="s">
         <v>55</v>
       </c>
       <c r="D9" s="43">
@@ -1698,8 +1698,8 @@
     </row>
     <row r="10" spans="1:31" ht="45.75">
       <c r="A10" s="43"/>
-      <c r="B10" s="44"/>
-      <c r="C10" s="45"/>
+      <c r="B10" s="45"/>
+      <c r="C10" s="55"/>
       <c r="D10" s="43"/>
       <c r="E10" s="12" t="s">
         <v>32</v>
@@ -1752,8 +1752,8 @@
     </row>
     <row r="11" spans="1:31" ht="45.75">
       <c r="A11" s="43"/>
-      <c r="B11" s="44"/>
-      <c r="C11" s="45"/>
+      <c r="B11" s="45"/>
+      <c r="C11" s="55"/>
       <c r="D11" s="43"/>
       <c r="E11" s="12" t="s">
         <v>19</v>
@@ -1818,10 +1818,10 @@
       <c r="A12" s="43">
         <v>145829</v>
       </c>
-      <c r="B12" s="44" t="s">
+      <c r="B12" s="45" t="s">
         <v>67</v>
       </c>
-      <c r="C12" s="45" t="s">
+      <c r="C12" s="55" t="s">
         <v>68</v>
       </c>
       <c r="D12" s="43">
@@ -1842,7 +1842,7 @@
       <c r="I12" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="J12" s="46" t="s">
+      <c r="J12" s="52" t="s">
         <v>26</v>
       </c>
       <c r="K12" s="10"/>
@@ -1860,7 +1860,7 @@
       <c r="S12" s="33"/>
       <c r="T12" s="21"/>
       <c r="U12" s="33"/>
-      <c r="W12" s="46" t="s">
+      <c r="W12" s="52" t="s">
         <v>27</v>
       </c>
       <c r="X12" s="10"/>
@@ -1878,8 +1878,8 @@
     </row>
     <row r="13" spans="1:31" ht="45.75">
       <c r="A13" s="43"/>
-      <c r="B13" s="44"/>
-      <c r="C13" s="45"/>
+      <c r="B13" s="45"/>
+      <c r="C13" s="55"/>
       <c r="D13" s="43"/>
       <c r="E13" s="12" t="s">
         <v>19</v>
@@ -1896,7 +1896,7 @@
       <c r="I13" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="J13" s="46"/>
+      <c r="J13" s="52"/>
       <c r="K13" s="10"/>
       <c r="L13" s="26" t="s">
         <v>27</v>
@@ -1920,7 +1920,7 @@
         <v>61</v>
       </c>
       <c r="U13" s="33"/>
-      <c r="W13" s="46"/>
+      <c r="W13" s="52"/>
       <c r="X13" s="10"/>
       <c r="Y13" s="10" t="s">
         <v>28</v>
@@ -1944,13 +1944,13 @@
       <c r="A14" s="43">
         <v>100344</v>
       </c>
-      <c r="B14" s="44" t="s">
+      <c r="B14" s="45" t="s">
         <v>75</v>
       </c>
-      <c r="C14" s="49" t="s">
+      <c r="C14" s="47" t="s">
         <v>76</v>
       </c>
-      <c r="D14" s="51">
+      <c r="D14" s="49">
         <v>996991</v>
       </c>
       <c r="E14" s="15" t="s">
@@ -1966,7 +1966,7 @@
         <v>50000</v>
       </c>
       <c r="I14" s="15"/>
-      <c r="J14" s="47" t="s">
+      <c r="J14" s="44" t="s">
         <v>79</v>
       </c>
       <c r="K14" s="10"/>
@@ -1984,7 +1984,7 @@
       <c r="S14" s="33"/>
       <c r="T14" s="21"/>
       <c r="U14" s="33"/>
-      <c r="W14" s="46" t="s">
+      <c r="W14" s="52" t="s">
         <v>27</v>
       </c>
       <c r="X14" s="10"/>
@@ -2002,9 +2002,9 @@
     </row>
     <row r="15" spans="1:31" ht="45.75">
       <c r="A15" s="43"/>
-      <c r="B15" s="44"/>
-      <c r="C15" s="49"/>
-      <c r="D15" s="52"/>
+      <c r="B15" s="45"/>
+      <c r="C15" s="47"/>
+      <c r="D15" s="50"/>
       <c r="E15" s="15" t="s">
         <v>32</v>
       </c>
@@ -2020,7 +2020,7 @@
       <c r="I15" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="J15" s="54"/>
+      <c r="J15" s="53"/>
       <c r="K15" s="10"/>
       <c r="L15" s="26" t="s">
         <v>27</v>
@@ -2036,7 +2036,7 @@
       <c r="S15" s="33"/>
       <c r="T15" s="21"/>
       <c r="U15" s="33"/>
-      <c r="W15" s="46"/>
+      <c r="W15" s="52"/>
       <c r="X15" s="10"/>
       <c r="Y15" s="10" t="s">
         <v>28</v>
@@ -2051,10 +2051,10 @@
       <c r="AE15" s="15"/>
     </row>
     <row r="16" spans="1:31" ht="45.75">
-      <c r="A16" s="47"/>
-      <c r="B16" s="48"/>
-      <c r="C16" s="50"/>
-      <c r="D16" s="53"/>
+      <c r="A16" s="44"/>
+      <c r="B16" s="46"/>
+      <c r="C16" s="48"/>
+      <c r="D16" s="51"/>
       <c r="E16" s="36" t="s">
         <v>83</v>
       </c>
@@ -2068,7 +2068,7 @@
         <v>60</v>
       </c>
       <c r="I16" s="15"/>
-      <c r="J16" s="55"/>
+      <c r="J16" s="54"/>
       <c r="K16" s="10"/>
       <c r="L16" s="26" t="s">
         <v>27</v>
@@ -2164,12 +2164,18 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="C14:C16"/>
-    <mergeCell ref="D14:D16"/>
-    <mergeCell ref="W14:W15"/>
-    <mergeCell ref="J14:J16"/>
+    <mergeCell ref="W6:W8"/>
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="B3:B5"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="J3:J5"/>
+    <mergeCell ref="W3:W5"/>
+    <mergeCell ref="A6:A8"/>
+    <mergeCell ref="B6:B8"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="J6:J8"/>
     <mergeCell ref="W12:W13"/>
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="B9:B11"/>
@@ -2182,18 +2188,12 @@
     <mergeCell ref="C12:C13"/>
     <mergeCell ref="D12:D13"/>
     <mergeCell ref="J12:J13"/>
-    <mergeCell ref="W6:W8"/>
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="B3:B5"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="J3:J5"/>
-    <mergeCell ref="W3:W5"/>
-    <mergeCell ref="A6:A8"/>
-    <mergeCell ref="B6:B8"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="J6:J8"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="D14:D16"/>
+    <mergeCell ref="W14:W15"/>
+    <mergeCell ref="J14:J16"/>
   </mergeCells>
   <dataValidations count="12">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD2:AD16" xr:uid="{2656783B-E017-4B69-B2BF-55ABED0028FD}">
@@ -2391,7 +2391,7 @@
       <c r="B3" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="45" t="s">
+      <c r="C3" s="55" t="s">
         <v>31</v>
       </c>
       <c r="D3" s="43">
@@ -2413,11 +2413,11 @@
       <c r="J3" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="K3" s="47" t="s">
+      <c r="K3" s="44" t="s">
         <v>94</v>
       </c>
       <c r="L3" s="10"/>
-      <c r="M3" s="47" t="s">
+      <c r="M3" s="44" t="s">
         <v>27</v>
       </c>
       <c r="N3" s="10"/>
@@ -2431,7 +2431,7 @@
     <row r="4" spans="1:19">
       <c r="A4" s="43"/>
       <c r="B4" s="43"/>
-      <c r="C4" s="45"/>
+      <c r="C4" s="55"/>
       <c r="D4" s="43"/>
       <c r="E4" s="12" t="s">
         <v>19</v>
@@ -2447,9 +2447,9 @@
       </c>
       <c r="I4" s="12"/>
       <c r="J4" s="12"/>
-      <c r="K4" s="54"/>
+      <c r="K4" s="53"/>
       <c r="L4" s="10"/>
-      <c r="M4" s="54"/>
+      <c r="M4" s="53"/>
       <c r="N4" s="10"/>
       <c r="O4" t="s">
         <v>28</v>
@@ -2467,7 +2467,7 @@
     <row r="5" spans="1:19">
       <c r="A5" s="43"/>
       <c r="B5" s="43"/>
-      <c r="C5" s="45"/>
+      <c r="C5" s="55"/>
       <c r="D5" s="43"/>
       <c r="E5" s="12" t="s">
         <v>19</v>
@@ -2487,9 +2487,9 @@
       <c r="J5" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="K5" s="55"/>
+      <c r="K5" s="54"/>
       <c r="L5" s="10"/>
-      <c r="M5" s="55"/>
+      <c r="M5" s="54"/>
       <c r="N5" s="10"/>
       <c r="O5" t="s">
         <v>28</v>
@@ -2511,7 +2511,7 @@
       <c r="B6" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="C6" s="45" t="s">
+      <c r="C6" s="55" t="s">
         <v>46</v>
       </c>
       <c r="D6" s="43">
@@ -2532,11 +2532,11 @@
       <c r="J6" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="K6" s="47" t="s">
+      <c r="K6" s="44" t="s">
         <v>49</v>
       </c>
       <c r="L6" s="10"/>
-      <c r="M6" s="47" t="s">
+      <c r="M6" s="44" t="s">
         <v>27</v>
       </c>
       <c r="N6" s="10"/>
@@ -2550,7 +2550,7 @@
     <row r="7" spans="1:19">
       <c r="A7" s="43"/>
       <c r="B7" s="43"/>
-      <c r="C7" s="45"/>
+      <c r="C7" s="55"/>
       <c r="D7" s="43"/>
       <c r="E7" s="12" t="s">
         <v>93</v>
@@ -2568,9 +2568,9 @@
       <c r="J7" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="K7" s="54"/>
+      <c r="K7" s="53"/>
       <c r="L7" s="10"/>
-      <c r="M7" s="54"/>
+      <c r="M7" s="53"/>
       <c r="N7" s="10"/>
       <c r="O7" t="s">
         <v>28</v>
@@ -2582,7 +2582,7 @@
     <row r="8" spans="1:19">
       <c r="A8" s="43"/>
       <c r="B8" s="43"/>
-      <c r="C8" s="45"/>
+      <c r="C8" s="55"/>
       <c r="D8" s="43"/>
       <c r="E8" s="12" t="s">
         <v>19</v>
@@ -2600,9 +2600,9 @@
       <c r="J8" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="K8" s="55"/>
+      <c r="K8" s="54"/>
       <c r="L8" s="10"/>
-      <c r="M8" s="55"/>
+      <c r="M8" s="54"/>
       <c r="N8" s="10"/>
       <c r="O8" t="s">
         <v>28</v>
@@ -2624,7 +2624,7 @@
       <c r="B9" s="43" t="s">
         <v>54</v>
       </c>
-      <c r="C9" s="45" t="s">
+      <c r="C9" s="55" t="s">
         <v>55</v>
       </c>
       <c r="D9" s="43">
@@ -2646,11 +2646,11 @@
       <c r="J9" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="K9" s="47" t="s">
+      <c r="K9" s="44" t="s">
         <v>58</v>
       </c>
       <c r="L9" s="10"/>
-      <c r="M9" s="47" t="s">
+      <c r="M9" s="44" t="s">
         <v>27</v>
       </c>
       <c r="N9" s="10"/>
@@ -2670,7 +2670,7 @@
     <row r="10" spans="1:19">
       <c r="A10" s="43"/>
       <c r="B10" s="43"/>
-      <c r="C10" s="45"/>
+      <c r="C10" s="55"/>
       <c r="D10" s="43"/>
       <c r="E10" s="12" t="s">
         <v>19</v>
@@ -2688,9 +2688,9 @@
       <c r="J10" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="K10" s="54"/>
+      <c r="K10" s="53"/>
       <c r="L10" s="10"/>
-      <c r="M10" s="54"/>
+      <c r="M10" s="53"/>
       <c r="N10" s="10"/>
       <c r="O10" t="s">
         <v>28</v>
@@ -2708,7 +2708,7 @@
     <row r="11" spans="1:19">
       <c r="A11" s="43"/>
       <c r="B11" s="43"/>
-      <c r="C11" s="45"/>
+      <c r="C11" s="55"/>
       <c r="D11" s="43"/>
       <c r="E11" s="12" t="s">
         <v>19</v>
@@ -2726,9 +2726,9 @@
       <c r="J11" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="K11" s="55"/>
+      <c r="K11" s="54"/>
       <c r="L11" s="10"/>
-      <c r="M11" s="55"/>
+      <c r="M11" s="54"/>
       <c r="N11" s="20"/>
       <c r="O11" t="s">
         <v>28</v>
@@ -2750,7 +2750,7 @@
       <c r="B12" s="43" t="s">
         <v>67</v>
       </c>
-      <c r="C12" s="45" t="s">
+      <c r="C12" s="55" t="s">
         <v>68</v>
       </c>
       <c r="D12" s="43">
@@ -2790,7 +2790,7 @@
     <row r="13" spans="1:19" ht="15.75" customHeight="1">
       <c r="A13" s="43"/>
       <c r="B13" s="43"/>
-      <c r="C13" s="45"/>
+      <c r="C13" s="55"/>
       <c r="D13" s="43"/>
       <c r="E13" s="12" t="s">
         <v>19</v>
@@ -2925,6 +2925,27 @@
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="K12:K13"/>
+    <mergeCell ref="M12:M13"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="D14:D16"/>
+    <mergeCell ref="M14:M15"/>
+    <mergeCell ref="K3:K5"/>
+    <mergeCell ref="M3:M5"/>
+    <mergeCell ref="K6:K8"/>
+    <mergeCell ref="M6:M8"/>
+    <mergeCell ref="K9:K11"/>
+    <mergeCell ref="M9:M11"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="D9:D11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D13"/>
     <mergeCell ref="A3:A5"/>
     <mergeCell ref="B3:B5"/>
     <mergeCell ref="C3:C5"/>
@@ -2933,27 +2954,6 @@
     <mergeCell ref="B6:B8"/>
     <mergeCell ref="C6:C8"/>
     <mergeCell ref="D6:D8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:B11"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="D9:D11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="K3:K5"/>
-    <mergeCell ref="M3:M5"/>
-    <mergeCell ref="K6:K8"/>
-    <mergeCell ref="M6:M8"/>
-    <mergeCell ref="K9:K11"/>
-    <mergeCell ref="M9:M11"/>
-    <mergeCell ref="K12:K13"/>
-    <mergeCell ref="M12:M13"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="C14:C16"/>
-    <mergeCell ref="D14:D16"/>
-    <mergeCell ref="M14:M15"/>
   </mergeCells>
   <dataValidations count="6">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E12" xr:uid="{8A6EECDF-213D-4435-9AB2-44F0897711E3}"/>
@@ -3683,54 +3683,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
-    <SharedWithUsers xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59">
-      <UserInfo>
-        <DisplayName>Suranga Karavita</DisplayName>
-        <AccountId>1730</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Hakshala David</DisplayName>
-        <AccountId>2305</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Afraa Mohamed</DisplayName>
-        <AccountId>2365</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Benjamin Keller</DisplayName>
-        <AccountId>1227</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Riad Meddeb</DisplayName>
-        <AccountId>9</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Stefano Pistolese</DisplayName>
-        <AccountId>772</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Pabasara Herath</DisplayName>
-        <AccountId>2367</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="dd25160c21e587dbb66203dfb8c7aa52">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="05ccd5be12d50c438f9536854e894bcb" ns2:_="" ns3:_="">
     <xsd:import namespace="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
@@ -3985,14 +3937,62 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
+    <SharedWithUsers xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59">
+      <UserInfo>
+        <DisplayName>Suranga Karavita</DisplayName>
+        <AccountId>1730</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Hakshala David</DisplayName>
+        <AccountId>2305</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Afraa Mohamed</DisplayName>
+        <AccountId>2365</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Benjamin Keller</DisplayName>
+        <AccountId>1227</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Riad Meddeb</DisplayName>
+        <AccountId>9</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Stefano Pistolese</DisplayName>
+        <AccountId>772</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Pabasara Herath</DisplayName>
+        <AccountId>2367</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{60C138E8-386B-4289-AC99-AD84197522D7}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{36D75D5F-5916-4E44-9F19-6C353537A8C9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B375FF7C-6204-4D0D-9323-0CEED1C8EC77}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B375FF7C-6204-4D0D-9323-0CEED1C8EC77}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{36D75D5F-5916-4E44-9F19-6C353537A8C9}"/>
 </file>
--- a/01_Input/00_CO Validation/Sri Lanka - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Sri Lanka - Energy Projects.xlsx
@@ -259,7 +259,7 @@
       <protection locked="0" hidden="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -404,22 +404,17 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="6" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="6" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -501,6 +496,66 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>CO validation update</author>
+  </authors>
+  <commentList>
+    <comment ref="K3" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="L3" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="K15" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="L15" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="K19" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="L19" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="K21" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="L21" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="K23" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="L23" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1044,15 +1099,11 @@
           <t>Installed capacity in MW for access/productive-use outputs</t>
         </is>
       </c>
-      <c r="K3" s="14" t="n">
+      <c r="K3" s="63" t="n">
         <v>0</v>
       </c>
       <c r="L3" s="63" t="n"/>
-      <c r="M3" s="64" t="inlineStr">
-        <is>
-          <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
-        </is>
-      </c>
+      <c r="M3" s="13" t="n"/>
       <c r="N3" s="10" t="n"/>
       <c r="O3" s="10" t="n"/>
       <c r="P3" s="43" t="n"/>
@@ -1075,20 +1126,40 @@
       <c r="AH3" s="14" t="n"/>
     </row>
     <row r="4" ht="45.75" customHeight="1">
-      <c r="A4" s="66" t="n"/>
-      <c r="B4" s="67" t="n"/>
-      <c r="C4" s="66" t="n"/>
-      <c r="D4" s="66" t="n"/>
-      <c r="E4" s="65" t="n"/>
-      <c r="F4" s="65" t="n"/>
-      <c r="G4" s="65" t="n"/>
-      <c r="H4" s="43" t="n"/>
+      <c r="A4" s="43" t="n">
+        <v>119366</v>
+      </c>
+      <c r="B4" s="45" t="inlineStr">
+        <is>
+          <t>Transitioning to sustainable energy uses for the agro-in</t>
+        </is>
+      </c>
+      <c r="C4" s="55" t="inlineStr">
+        <is>
+          <t>http://open.undp.org/projects/00119366</t>
+        </is>
+      </c>
+      <c r="D4" s="43" t="n">
+        <v>1007201</v>
+      </c>
+      <c r="E4" s="64" t="n"/>
+      <c r="F4" s="64" t="n"/>
+      <c r="G4" s="64" t="n"/>
+      <c r="H4" s="43" t="inlineStr">
+        <is>
+          <t>Non-VF</t>
+        </is>
+      </c>
       <c r="I4" s="12" t="inlineStr">
         <is>
           <t>Capacity Building Training</t>
         </is>
       </c>
-      <c r="J4" s="66" t="n"/>
+      <c r="J4" s="12" t="inlineStr">
+        <is>
+          <t>Number of farmers</t>
+        </is>
+      </c>
       <c r="K4" s="12" t="n">
         <v>0</v>
       </c>
@@ -1117,7 +1188,7 @@
       <c r="T4" s="43" t="n"/>
       <c r="U4" s="43" t="n"/>
       <c r="V4" s="33" t="n"/>
-      <c r="W4" s="66" t="n"/>
+      <c r="W4" s="43" t="n"/>
       <c r="X4" s="33" t="n"/>
       <c r="Z4" s="43" t="inlineStr">
         <is>
@@ -1142,20 +1213,16 @@
       <c r="AH4" s="12" t="n"/>
     </row>
     <row r="5" ht="45.75" customHeight="1">
-      <c r="A5" s="68" t="n"/>
-      <c r="B5" s="69" t="n"/>
-      <c r="C5" s="68" t="n"/>
-      <c r="D5" s="68" t="n"/>
-      <c r="E5" s="66" t="n"/>
-      <c r="F5" s="66" t="n"/>
-      <c r="G5" s="66" t="n"/>
-      <c r="H5" s="66" t="n"/>
       <c r="I5" s="12" t="inlineStr">
         <is>
           <t>Capacity Building Training</t>
         </is>
       </c>
-      <c r="J5" s="68" t="n"/>
+      <c r="J5" s="12" t="inlineStr">
+        <is>
+          <t>Capacity of staff of five provincial councils built on monioring energy and GHG savings</t>
+        </is>
+      </c>
       <c r="K5" s="12" t="n">
         <v>0</v>
       </c>
@@ -1163,7 +1230,6 @@
         <v>125</v>
       </c>
       <c r="M5" s="12" t="n"/>
-      <c r="N5" s="66" t="n"/>
       <c r="O5" s="10" t="n"/>
       <c r="P5" s="43" t="n"/>
       <c r="Q5" s="32" t="inlineStr">
@@ -1176,9 +1242,8 @@
       <c r="T5" s="43" t="n"/>
       <c r="U5" s="43" t="n"/>
       <c r="V5" s="33" t="n"/>
-      <c r="W5" s="68" t="n"/>
+      <c r="W5" s="43" t="n"/>
       <c r="X5" s="33" t="n"/>
-      <c r="Z5" s="66" t="n"/>
       <c r="AA5" s="10" t="n"/>
       <c r="AB5" s="10" t="inlineStr">
         <is>
@@ -1205,14 +1270,6 @@
       <c r="AH5" s="12" t="n"/>
     </row>
     <row r="6" ht="45.75" customHeight="1">
-      <c r="A6" s="68" t="n"/>
-      <c r="B6" s="69" t="n"/>
-      <c r="C6" s="68" t="n"/>
-      <c r="D6" s="68" t="n"/>
-      <c r="E6" s="68" t="n"/>
-      <c r="F6" s="68" t="n"/>
-      <c r="G6" s="68" t="n"/>
-      <c r="H6" s="68" t="n"/>
       <c r="I6" s="12" t="inlineStr">
         <is>
           <t>Policy or Regulatory Framework</t>
@@ -1234,7 +1291,6 @@
           <t>Around 1.2 million (indirect beneficiaries) farmers will benefit from five provinces from the energy plans that has RE and EE</t>
         </is>
       </c>
-      <c r="N6" s="68" t="n"/>
       <c r="O6" s="10" t="n"/>
       <c r="P6" s="43" t="n"/>
       <c r="Q6" s="32" t="inlineStr">
@@ -1267,7 +1323,6 @@
       <c r="X6" s="33" t="n">
         <v>1200000</v>
       </c>
-      <c r="Z6" s="68" t="n"/>
       <c r="AA6" s="10" t="n"/>
       <c r="AB6" s="10" t="inlineStr">
         <is>
@@ -1300,20 +1355,40 @@
       </c>
     </row>
     <row r="7" ht="45.75" customHeight="1">
-      <c r="A7" s="66" t="n"/>
-      <c r="B7" s="67" t="n"/>
-      <c r="C7" s="66" t="n"/>
-      <c r="D7" s="66" t="n"/>
-      <c r="E7" s="65" t="n"/>
-      <c r="F7" s="65" t="n"/>
-      <c r="G7" s="65" t="n"/>
-      <c r="H7" s="43" t="n"/>
+      <c r="A7" s="43" t="n">
+        <v>134410</v>
+      </c>
+      <c r="B7" s="45" t="inlineStr">
+        <is>
+          <t>MP Projects Sri Lanka</t>
+        </is>
+      </c>
+      <c r="C7" s="55" t="inlineStr">
+        <is>
+          <t>http://open.undp.org/projects/00134410</t>
+        </is>
+      </c>
+      <c r="D7" s="43" t="n">
+        <v>261353</v>
+      </c>
+      <c r="E7" s="64" t="n"/>
+      <c r="F7" s="64" t="n"/>
+      <c r="G7" s="64" t="n"/>
+      <c r="H7" s="43" t="inlineStr">
+        <is>
+          <t>Non-VF</t>
+        </is>
+      </c>
       <c r="I7" s="12" t="inlineStr">
         <is>
           <t>Capacity Building Training</t>
         </is>
       </c>
-      <c r="J7" s="66" t="n"/>
+      <c r="J7" s="15" t="inlineStr">
+        <is>
+          <t>Number of students/year</t>
+        </is>
+      </c>
       <c r="K7" s="12" t="n">
         <v>0</v>
       </c>
@@ -1342,7 +1417,7 @@
       <c r="T7" s="43" t="n"/>
       <c r="U7" s="43" t="n"/>
       <c r="V7" s="33" t="n"/>
-      <c r="W7" s="66" t="n"/>
+      <c r="W7" s="43" t="n"/>
       <c r="X7" s="33" t="n"/>
       <c r="Z7" s="43" t="inlineStr">
         <is>
@@ -1367,20 +1442,16 @@
       <c r="AH7" s="10" t="n"/>
     </row>
     <row r="8" ht="45.75" customHeight="1">
-      <c r="A8" s="68" t="n"/>
-      <c r="B8" s="69" t="n"/>
-      <c r="C8" s="68" t="n"/>
-      <c r="D8" s="68" t="n"/>
-      <c r="E8" s="66" t="n"/>
-      <c r="F8" s="66" t="n"/>
-      <c r="G8" s="66" t="n"/>
-      <c r="H8" s="66" t="n"/>
       <c r="I8" s="12" t="inlineStr">
         <is>
           <t>Capacity Building Training</t>
         </is>
       </c>
-      <c r="J8" s="68" t="n"/>
+      <c r="J8" s="15" t="inlineStr">
+        <is>
+          <t>Number of trainees</t>
+        </is>
+      </c>
       <c r="K8" s="12" t="n">
         <v>0</v>
       </c>
@@ -1392,7 +1463,6 @@
           <t>500 RAC sector technicians will be trained</t>
         </is>
       </c>
-      <c r="N8" s="66" t="n"/>
       <c r="O8" s="10" t="n"/>
       <c r="P8" s="43" t="n"/>
       <c r="Q8" s="32" t="inlineStr">
@@ -1405,9 +1475,8 @@
       <c r="T8" s="43" t="n"/>
       <c r="U8" s="43" t="n"/>
       <c r="V8" s="33" t="n"/>
-      <c r="W8" s="68" t="n"/>
+      <c r="W8" s="43" t="n"/>
       <c r="X8" s="33" t="n"/>
-      <c r="Z8" s="66" t="n"/>
       <c r="AA8" s="10" t="n"/>
       <c r="AB8" s="10" t="inlineStr">
         <is>
@@ -1426,14 +1495,6 @@
       <c r="AH8" s="12" t="n"/>
     </row>
     <row r="9" ht="45.75" customHeight="1">
-      <c r="A9" s="68" t="n"/>
-      <c r="B9" s="69" t="n"/>
-      <c r="C9" s="68" t="n"/>
-      <c r="D9" s="68" t="n"/>
-      <c r="E9" s="68" t="n"/>
-      <c r="F9" s="68" t="n"/>
-      <c r="G9" s="68" t="n"/>
-      <c r="H9" s="68" t="n"/>
       <c r="I9" s="12" t="inlineStr">
         <is>
           <t>Capacity Building Training</t>
@@ -1455,7 +1516,6 @@
           <t>Around 30 govt officals will be trained</t>
         </is>
       </c>
-      <c r="N9" s="68" t="n"/>
       <c r="O9" s="10" t="n"/>
       <c r="P9" s="43" t="n"/>
       <c r="Q9" s="32" t="inlineStr">
@@ -1470,7 +1530,6 @@
       <c r="V9" s="33" t="n"/>
       <c r="W9" s="43" t="n"/>
       <c r="X9" s="33" t="n"/>
-      <c r="Z9" s="68" t="n"/>
       <c r="AA9" s="10" t="n"/>
       <c r="AB9" s="10" t="inlineStr">
         <is>
@@ -1497,20 +1556,40 @@
       <c r="AH9" s="12" t="n"/>
     </row>
     <row r="10" ht="45.75" customHeight="1">
-      <c r="A10" s="66" t="n"/>
-      <c r="B10" s="67" t="n"/>
-      <c r="C10" s="66" t="n"/>
-      <c r="D10" s="66" t="n"/>
-      <c r="E10" s="65" t="n"/>
-      <c r="F10" s="65" t="n"/>
-      <c r="G10" s="65" t="n"/>
-      <c r="H10" s="43" t="n"/>
+      <c r="A10" s="43" t="n">
+        <v>142290</v>
+      </c>
+      <c r="B10" s="45" t="inlineStr">
+        <is>
+          <t>Climate Promise: From Pledge to Impact</t>
+        </is>
+      </c>
+      <c r="C10" s="55" t="inlineStr">
+        <is>
+          <t>http://open.undp.org/projects/00142290</t>
+        </is>
+      </c>
+      <c r="D10" s="43" t="n">
+        <v>324000</v>
+      </c>
+      <c r="E10" s="64" t="n"/>
+      <c r="F10" s="64" t="n"/>
+      <c r="G10" s="64" t="n"/>
+      <c r="H10" s="43" t="inlineStr">
+        <is>
+          <t>Non-VF</t>
+        </is>
+      </c>
       <c r="I10" s="12" t="inlineStr">
         <is>
           <t>Policy or Regulatory Framework</t>
         </is>
       </c>
-      <c r="J10" s="66" t="n"/>
+      <c r="J10" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Number of Inclusive policy, strategies, plans and regulatory frameworks (national, sectoral or sub-national) in place to support NDC implementation and drive green recovery</t>
+        </is>
+      </c>
       <c r="K10" s="12" t="n">
         <v>0</v>
       </c>
@@ -1552,7 +1631,11 @@
         </is>
       </c>
       <c r="V10" s="33" t="n"/>
-      <c r="W10" s="66" t="n"/>
+      <c r="W10" s="43" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
       <c r="X10" s="33" t="n"/>
       <c r="Z10" s="43" t="inlineStr">
         <is>
@@ -1589,20 +1672,16 @@
       <c r="AH10" s="12" t="n"/>
     </row>
     <row r="11" ht="45.75" customHeight="1">
-      <c r="A11" s="68" t="n"/>
-      <c r="B11" s="69" t="n"/>
-      <c r="C11" s="68" t="n"/>
-      <c r="D11" s="68" t="n"/>
-      <c r="E11" s="66" t="n"/>
-      <c r="F11" s="66" t="n"/>
-      <c r="G11" s="66" t="n"/>
-      <c r="H11" s="66" t="n"/>
       <c r="I11" s="12" t="inlineStr">
         <is>
           <t>Capacity Building Training</t>
         </is>
       </c>
-      <c r="J11" s="68" t="n"/>
+      <c r="J11" s="12" t="inlineStr">
+        <is>
+          <t>Number of trainees</t>
+        </is>
+      </c>
       <c r="K11" s="12" t="n">
         <v>0</v>
       </c>
@@ -1614,7 +1693,6 @@
           <t>400 govt officials trained</t>
         </is>
       </c>
-      <c r="N11" s="66" t="n"/>
       <c r="O11" s="10" t="n"/>
       <c r="P11" s="43" t="n"/>
       <c r="Q11" s="32" t="inlineStr">
@@ -1627,9 +1705,8 @@
       <c r="T11" s="43" t="n"/>
       <c r="U11" s="43" t="n"/>
       <c r="V11" s="33" t="n"/>
-      <c r="W11" s="68" t="n"/>
+      <c r="W11" s="43" t="n"/>
       <c r="X11" s="33" t="n"/>
-      <c r="Z11" s="66" t="n"/>
       <c r="AA11" s="10" t="n"/>
       <c r="AB11" s="10" t="inlineStr">
         <is>
@@ -1656,14 +1733,6 @@
       <c r="AH11" s="12" t="n"/>
     </row>
     <row r="12" ht="45.75" customHeight="1">
-      <c r="A12" s="68" t="n"/>
-      <c r="B12" s="69" t="n"/>
-      <c r="C12" s="68" t="n"/>
-      <c r="D12" s="68" t="n"/>
-      <c r="E12" s="68" t="n"/>
-      <c r="F12" s="68" t="n"/>
-      <c r="G12" s="68" t="n"/>
-      <c r="H12" s="68" t="n"/>
       <c r="I12" s="12" t="inlineStr">
         <is>
           <t>Policy or Regulatory Framework</t>
@@ -1685,7 +1754,6 @@
           <t>Platform for youth, women and multistakeholder developed to lead NDC development and implementation</t>
         </is>
       </c>
-      <c r="N12" s="68" t="n"/>
       <c r="O12" s="10" t="n"/>
       <c r="P12" s="43" t="n"/>
       <c r="Q12" s="32" t="inlineStr">
@@ -1716,7 +1784,6 @@
         </is>
       </c>
       <c r="X12" s="33" t="n"/>
-      <c r="Z12" s="68" t="n"/>
       <c r="AA12" s="23" t="n"/>
       <c r="AB12" s="10" t="inlineStr">
         <is>
@@ -1747,20 +1814,40 @@
       <c r="AH12" s="12" t="n"/>
     </row>
     <row r="13" ht="45.75" customHeight="1">
-      <c r="A13" s="68" t="n"/>
-      <c r="B13" s="69" t="n"/>
-      <c r="C13" s="68" t="n"/>
-      <c r="D13" s="68" t="n"/>
-      <c r="E13" s="65" t="n"/>
-      <c r="F13" s="65" t="n"/>
-      <c r="G13" s="65" t="n"/>
-      <c r="H13" s="43" t="n"/>
+      <c r="A13" s="43" t="n">
+        <v>145829</v>
+      </c>
+      <c r="B13" s="45" t="inlineStr">
+        <is>
+          <t>Mainstreaming E-Mobility Through the Conversion of Tuk-T</t>
+        </is>
+      </c>
+      <c r="C13" s="55" t="inlineStr">
+        <is>
+          <t>http://open.undp.org/projects/00145829</t>
+        </is>
+      </c>
+      <c r="D13" s="43" t="n">
+        <v>1151772</v>
+      </c>
+      <c r="E13" s="64" t="n"/>
+      <c r="F13" s="64" t="n"/>
+      <c r="G13" s="64" t="n"/>
+      <c r="H13" s="43" t="inlineStr">
+        <is>
+          <t>Non-VF</t>
+        </is>
+      </c>
       <c r="I13" s="12" t="inlineStr">
         <is>
           <t>Transportation and E-mobility Services</t>
         </is>
       </c>
-      <c r="J13" s="68" t="n"/>
+      <c r="J13" s="12" t="inlineStr">
+        <is>
+          <t>Number of passengers</t>
+        </is>
+      </c>
       <c r="K13" s="12" t="n">
         <v>0</v>
       </c>
@@ -1789,7 +1876,7 @@
       <c r="T13" s="43" t="n"/>
       <c r="U13" s="43" t="n"/>
       <c r="V13" s="33" t="n"/>
-      <c r="W13" s="68" t="n"/>
+      <c r="W13" s="43" t="n"/>
       <c r="X13" s="33" t="n"/>
       <c r="Z13" s="52" t="inlineStr">
         <is>
@@ -1814,14 +1901,6 @@
       <c r="AH13" s="12" t="n"/>
     </row>
     <row r="14" ht="45.75" customHeight="1">
-      <c r="A14" s="68" t="n"/>
-      <c r="B14" s="69" t="n"/>
-      <c r="C14" s="68" t="n"/>
-      <c r="D14" s="68" t="n"/>
-      <c r="E14" s="68" t="n"/>
-      <c r="F14" s="68" t="n"/>
-      <c r="G14" s="68" t="n"/>
-      <c r="H14" s="68" t="n"/>
       <c r="I14" s="12" t="inlineStr">
         <is>
           <t>Policy or Regulatory Framework</t>
@@ -1843,7 +1922,6 @@
           <t>1.15 million existing fuel three wheelers now have the opportunity to be legally registereted as electric three wheelers</t>
         </is>
       </c>
-      <c r="N14" s="68" t="n"/>
       <c r="O14" s="10" t="n"/>
       <c r="P14" s="43" t="n"/>
       <c r="Q14" s="32" t="inlineStr">
@@ -1874,7 +1952,6 @@
         </is>
       </c>
       <c r="X14" s="33" t="n"/>
-      <c r="Z14" s="68" t="n"/>
       <c r="AA14" s="10" t="n"/>
       <c r="AB14" s="10" t="inlineStr">
         <is>
@@ -1905,30 +1982,21 @@
       <c r="AH14" s="12" t="n"/>
     </row>
     <row r="15" ht="45.75" customHeight="1">
-      <c r="A15" s="66" t="n"/>
-      <c r="B15" s="67" t="n"/>
-      <c r="C15" s="66" t="n"/>
-      <c r="D15" s="66" t="n"/>
-      <c r="E15" s="68" t="n"/>
-      <c r="F15" s="68" t="n"/>
-      <c r="G15" s="68" t="n"/>
-      <c r="H15" s="68" t="n"/>
       <c r="I15" s="12" t="inlineStr">
         <is>
           <t>Energy (MW added)</t>
         </is>
       </c>
-      <c r="J15" s="66" t="n"/>
-      <c r="K15" s="12" t="n">
+      <c r="J15" s="12" t="inlineStr">
+        <is>
+          <t>Installed capacity in MW for access/productive-use outputs</t>
+        </is>
+      </c>
+      <c r="K15" s="62" t="n">
         <v>0</v>
       </c>
       <c r="L15" s="62" t="n"/>
-      <c r="M15" s="62" t="inlineStr">
-        <is>
-          <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
-        </is>
-      </c>
-      <c r="N15" s="68" t="n"/>
+      <c r="M15" s="12" t="n"/>
       <c r="O15" s="10" t="n"/>
       <c r="P15" s="43" t="n"/>
       <c r="Q15" s="32" t="n"/>
@@ -1937,9 +2005,8 @@
       <c r="T15" s="43" t="n"/>
       <c r="U15" s="43" t="n"/>
       <c r="V15" s="33" t="n"/>
-      <c r="W15" s="68" t="n"/>
+      <c r="W15" s="43" t="n"/>
       <c r="X15" s="33" t="n"/>
-      <c r="Z15" s="68" t="n"/>
       <c r="AA15" s="10" t="n"/>
       <c r="AB15" s="10" t="n"/>
       <c r="AC15" s="10" t="n"/>
@@ -1950,20 +2017,40 @@
       <c r="AH15" s="12" t="n"/>
     </row>
     <row r="16" ht="45.75" customHeight="1">
-      <c r="A16" s="68" t="n"/>
-      <c r="B16" s="69" t="n"/>
-      <c r="C16" s="68" t="n"/>
-      <c r="D16" s="68" t="n"/>
-      <c r="E16" s="70" t="n"/>
-      <c r="F16" s="70" t="n"/>
-      <c r="G16" s="70" t="n"/>
-      <c r="H16" s="49" t="n"/>
+      <c r="A16" s="43" t="n">
+        <v>100344</v>
+      </c>
+      <c r="B16" s="45" t="inlineStr">
+        <is>
+          <t>Enhancing Food and Energy Security through the promotion of Green Technologies</t>
+        </is>
+      </c>
+      <c r="C16" s="47" t="inlineStr">
+        <is>
+          <t>https://open.undp.org/projects/00100344</t>
+        </is>
+      </c>
+      <c r="D16" s="49" t="n">
+        <v>996991</v>
+      </c>
+      <c r="E16" s="65" t="n"/>
+      <c r="F16" s="65" t="n"/>
+      <c r="G16" s="65" t="n"/>
+      <c r="H16" s="49" t="inlineStr">
+        <is>
+          <t>Non-VF</t>
+        </is>
+      </c>
       <c r="I16" s="15" t="inlineStr">
         <is>
           <t>Agriculture and Food System</t>
         </is>
       </c>
-      <c r="J16" s="68" t="n"/>
+      <c r="J16" s="15" t="inlineStr">
+        <is>
+          <t>Number of beneficiaries with access to green/sustainable technologies</t>
+        </is>
+      </c>
       <c r="K16" s="15" t="n">
         <v>270</v>
       </c>
@@ -2013,14 +2100,6 @@
       <c r="AH16" s="15" t="n"/>
     </row>
     <row r="17" ht="45.75" customHeight="1">
-      <c r="A17" s="66" t="n"/>
-      <c r="B17" s="67" t="n"/>
-      <c r="C17" s="66" t="n"/>
-      <c r="D17" s="66" t="n"/>
-      <c r="E17" s="66" t="n"/>
-      <c r="F17" s="66" t="n"/>
-      <c r="G17" s="66" t="n"/>
-      <c r="H17" s="66" t="n"/>
       <c r="I17" s="15" t="inlineStr">
         <is>
           <t>Capacity Building Training</t>
@@ -2042,7 +2121,6 @@
           <t>Roughly 80,000 small holder farmers will be trained</t>
         </is>
       </c>
-      <c r="N17" s="66" t="n"/>
       <c r="O17" s="10" t="n"/>
       <c r="P17" s="43" t="n"/>
       <c r="Q17" s="32" t="inlineStr">
@@ -2057,7 +2135,6 @@
       <c r="V17" s="33" t="n"/>
       <c r="W17" s="43" t="n"/>
       <c r="X17" s="33" t="n"/>
-      <c r="Z17" s="68" t="n"/>
       <c r="AA17" s="10" t="n"/>
       <c r="AB17" s="10" t="inlineStr">
         <is>
@@ -2076,14 +2153,6 @@
       <c r="AH17" s="15" t="n"/>
     </row>
     <row r="18" ht="30.75" customHeight="1">
-      <c r="A18" s="68" t="n"/>
-      <c r="B18" s="69" t="n"/>
-      <c r="C18" s="68" t="n"/>
-      <c r="D18" s="68" t="n"/>
-      <c r="E18" s="68" t="n"/>
-      <c r="F18" s="68" t="n"/>
-      <c r="G18" s="68" t="n"/>
-      <c r="H18" s="68" t="n"/>
       <c r="I18" s="36" t="inlineStr">
         <is>
           <t>Entrepreneurship Training</t>
@@ -2101,7 +2170,6 @@
         <v>60</v>
       </c>
       <c r="M18" s="15" t="n"/>
-      <c r="N18" s="68" t="n"/>
       <c r="O18" s="10" t="n"/>
       <c r="P18" s="43" t="n"/>
       <c r="Q18" s="32" t="inlineStr">
@@ -2135,14 +2203,6 @@
       <c r="AH18" s="15" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="68" t="n"/>
-      <c r="B19" s="69" t="n"/>
-      <c r="C19" s="68" t="n"/>
-      <c r="D19" s="68" t="n"/>
-      <c r="E19" s="68" t="n"/>
-      <c r="F19" s="68" t="n"/>
-      <c r="G19" s="68" t="n"/>
-      <c r="H19" s="68" t="n"/>
       <c r="I19" s="36" t="inlineStr">
         <is>
           <t>Energy (MW added)</t>
@@ -2153,16 +2213,11 @@
           <t>Installed capacity in MW for access/productive-use outputs</t>
         </is>
       </c>
-      <c r="K19" s="15" t="n">
+      <c r="K19" s="62" t="n">
         <v>0</v>
       </c>
       <c r="L19" s="62" t="n"/>
-      <c r="M19" s="62" t="inlineStr">
-        <is>
-          <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
-        </is>
-      </c>
-      <c r="N19" s="68" t="n"/>
+      <c r="M19" s="15" t="n"/>
       <c r="O19" s="10" t="n"/>
       <c r="P19" s="43" t="n"/>
       <c r="Q19" s="32" t="n"/>
@@ -2200,9 +2255,9 @@
       <c r="D20" s="42" t="n">
         <v>43615</v>
       </c>
-      <c r="E20" s="71" t="n"/>
-      <c r="F20" s="71" t="n"/>
-      <c r="G20" s="71" t="n"/>
+      <c r="E20" s="66" t="n"/>
+      <c r="F20" s="66" t="n"/>
+      <c r="G20" s="66" t="n"/>
       <c r="H20" s="42" t="inlineStr">
         <is>
           <t>Non-VF</t>
@@ -2249,15 +2304,10 @@
           <t>Installed capacity in MW for access/productive-use outputs</t>
         </is>
       </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="72" t="n"/>
-      <c r="M21" s="72" t="inlineStr">
-        <is>
-          <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
-        </is>
-      </c>
+      <c r="K21" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="67" t="n"/>
       <c r="N21" s="37" t="n"/>
     </row>
     <row r="22">
@@ -2277,9 +2327,9 @@
       <c r="D22" s="34" t="n">
         <v>24533</v>
       </c>
-      <c r="E22" s="73" t="n"/>
-      <c r="F22" s="73" t="n"/>
-      <c r="G22" s="73" t="n"/>
+      <c r="E22" s="68" t="n"/>
+      <c r="F22" s="68" t="n"/>
+      <c r="G22" s="68" t="n"/>
       <c r="H22" s="34" t="inlineStr">
         <is>
           <t>Non-VF</t>
@@ -2326,50 +2376,13 @@
           <t>Installed capacity in MW for access/productive-use outputs</t>
         </is>
       </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" s="72" t="n"/>
-      <c r="M23" s="72" t="inlineStr">
-        <is>
-          <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
-        </is>
-      </c>
+      <c r="K23" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="67" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="30">
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="J3:J5"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="W9:W11"/>
-    <mergeCell ref="D14:D16"/>
-    <mergeCell ref="D9:D11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="B3:B5"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="J14:J16"/>
-    <mergeCell ref="W12:W13"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="W6:W8"/>
-    <mergeCell ref="W14:W15"/>
-    <mergeCell ref="J12:J13"/>
-    <mergeCell ref="C14:C16"/>
-    <mergeCell ref="J6:J8"/>
-    <mergeCell ref="A6:A8"/>
-    <mergeCell ref="J9:J11"/>
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="B9:B11"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="W3:W5"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="B6:B8"/>
-  </mergeCells>
-  <dataValidations count="15">
+  <dataValidations count="13">
     <dataValidation sqref="AD2:AD16" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Electricity Access, Energy Efficiency, Renewable EnergyEnergy Infrastructure,   Transport, Digital &amp; Data, Clean Cooking, Decarbonization, Hydrogen, Off-Grid, On-Grid"</formula1>
     </dataValidation>
@@ -2409,17 +2422,12 @@
     <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
       <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
-      <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
-      <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
-    </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -2665,10 +2673,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="66" t="n"/>
-      <c r="B4" s="66" t="n"/>
-      <c r="C4" s="66" t="n"/>
-      <c r="D4" s="66" t="n"/>
+      <c r="A4" s="69" t="n"/>
+      <c r="B4" s="69" t="n"/>
+      <c r="C4" s="69" t="n"/>
+      <c r="D4" s="69" t="n"/>
       <c r="E4" s="12" t="inlineStr">
         <is>
           <t>Policy or Regulatory Framework</t>
@@ -2687,9 +2695,9 @@
       </c>
       <c r="I4" s="12" t="n"/>
       <c r="J4" s="12" t="n"/>
-      <c r="K4" s="66" t="n"/>
+      <c r="K4" s="69" t="n"/>
       <c r="L4" s="10" t="n"/>
-      <c r="M4" s="66" t="n"/>
+      <c r="M4" s="69" t="n"/>
       <c r="N4" s="10" t="n"/>
       <c r="O4" t="inlineStr">
         <is>
@@ -2713,10 +2721,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="68" t="n"/>
-      <c r="B5" s="68" t="n"/>
-      <c r="C5" s="68" t="n"/>
-      <c r="D5" s="68" t="n"/>
+      <c r="A5" s="70" t="n"/>
+      <c r="B5" s="70" t="n"/>
+      <c r="C5" s="70" t="n"/>
+      <c r="D5" s="70" t="n"/>
       <c r="E5" s="12" t="inlineStr">
         <is>
           <t>Policy or Regulatory Framework</t>
@@ -2741,9 +2749,9 @@
           <t>Around 1.2 million farmers will benefit from five provinces from the energy plans that has RE and EE</t>
         </is>
       </c>
-      <c r="K5" s="68" t="n"/>
+      <c r="K5" s="70" t="n"/>
       <c r="L5" s="10" t="n"/>
-      <c r="M5" s="68" t="n"/>
+      <c r="M5" s="70" t="n"/>
       <c r="N5" s="10" t="n"/>
       <c r="O5" t="inlineStr">
         <is>
@@ -2828,10 +2836,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="66" t="n"/>
-      <c r="B7" s="66" t="n"/>
-      <c r="C7" s="66" t="n"/>
-      <c r="D7" s="66" t="n"/>
+      <c r="A7" s="69" t="n"/>
+      <c r="B7" s="69" t="n"/>
+      <c r="C7" s="69" t="n"/>
+      <c r="D7" s="69" t="n"/>
       <c r="E7" s="12" t="inlineStr">
         <is>
           <t>Capacity Training</t>
@@ -2854,9 +2862,9 @@
           <t>500 RAC sector technicians will be trained</t>
         </is>
       </c>
-      <c r="K7" s="66" t="n"/>
+      <c r="K7" s="69" t="n"/>
       <c r="L7" s="10" t="n"/>
-      <c r="M7" s="66" t="n"/>
+      <c r="M7" s="69" t="n"/>
       <c r="N7" s="10" t="n"/>
       <c r="O7" t="inlineStr">
         <is>
@@ -2870,10 +2878,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="68" t="n"/>
-      <c r="B8" s="68" t="n"/>
-      <c r="C8" s="68" t="n"/>
-      <c r="D8" s="68" t="n"/>
+      <c r="A8" s="70" t="n"/>
+      <c r="B8" s="70" t="n"/>
+      <c r="C8" s="70" t="n"/>
+      <c r="D8" s="70" t="n"/>
       <c r="E8" s="12" t="inlineStr">
         <is>
           <t>Policy or Regulatory Framework</t>
@@ -2896,9 +2904,9 @@
           <t>Around 30 govt officals will be trained</t>
         </is>
       </c>
-      <c r="K8" s="68" t="n"/>
+      <c r="K8" s="70" t="n"/>
       <c r="L8" s="10" t="n"/>
-      <c r="M8" s="68" t="n"/>
+      <c r="M8" s="70" t="n"/>
       <c r="N8" s="10" t="n"/>
       <c r="O8" t="inlineStr">
         <is>
@@ -2995,10 +3003,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="66" t="n"/>
-      <c r="B10" s="66" t="n"/>
-      <c r="C10" s="66" t="n"/>
-      <c r="D10" s="66" t="n"/>
+      <c r="A10" s="69" t="n"/>
+      <c r="B10" s="69" t="n"/>
+      <c r="C10" s="69" t="n"/>
+      <c r="D10" s="69" t="n"/>
       <c r="E10" s="12" t="inlineStr">
         <is>
           <t>Policy or Regulatory Framework</t>
@@ -3021,9 +3029,9 @@
           <t>400 govt officials trained</t>
         </is>
       </c>
-      <c r="K10" s="66" t="n"/>
+      <c r="K10" s="69" t="n"/>
       <c r="L10" s="10" t="n"/>
-      <c r="M10" s="66" t="n"/>
+      <c r="M10" s="69" t="n"/>
       <c r="N10" s="10" t="n"/>
       <c r="O10" t="inlineStr">
         <is>
@@ -3047,10 +3055,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="68" t="n"/>
-      <c r="B11" s="68" t="n"/>
-      <c r="C11" s="68" t="n"/>
-      <c r="D11" s="68" t="n"/>
+      <c r="A11" s="70" t="n"/>
+      <c r="B11" s="70" t="n"/>
+      <c r="C11" s="70" t="n"/>
+      <c r="D11" s="70" t="n"/>
       <c r="E11" s="12" t="inlineStr">
         <is>
           <t>Policy or Regulatory Framework</t>
@@ -3073,9 +3081,9 @@
           <t>Platform for youth, women and multistakeholder developed to lead NDC development and implementation</t>
         </is>
       </c>
-      <c r="K11" s="68" t="n"/>
+      <c r="K11" s="70" t="n"/>
       <c r="L11" s="10" t="n"/>
-      <c r="M11" s="68" t="n"/>
+      <c r="M11" s="70" t="n"/>
       <c r="N11" s="20" t="n"/>
       <c r="O11" t="inlineStr">
         <is>
@@ -3161,10 +3169,10 @@
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="68" t="n"/>
-      <c r="B13" s="68" t="n"/>
-      <c r="C13" s="68" t="n"/>
-      <c r="D13" s="68" t="n"/>
+      <c r="A13" s="70" t="n"/>
+      <c r="B13" s="70" t="n"/>
+      <c r="C13" s="70" t="n"/>
+      <c r="D13" s="70" t="n"/>
       <c r="E13" s="12" t="inlineStr">
         <is>
           <t>Policy or Regulatory Framework</t>
@@ -3187,9 +3195,9 @@
           <t>1.15 million existing fuel three wheelers now have the opportunity to be legally registereted as electric three wheelers</t>
         </is>
       </c>
-      <c r="K13" s="68" t="n"/>
+      <c r="K13" s="70" t="n"/>
       <c r="L13" s="10" t="n"/>
-      <c r="M13" s="68" t="n"/>
+      <c r="M13" s="70" t="n"/>
       <c r="N13" s="10" t="n"/>
       <c r="O13" t="inlineStr">
         <is>
@@ -3261,10 +3269,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="66" t="n"/>
-      <c r="B15" s="66" t="n"/>
-      <c r="C15" s="66" t="n"/>
-      <c r="D15" s="66" t="n"/>
+      <c r="A15" s="69" t="n"/>
+      <c r="B15" s="69" t="n"/>
+      <c r="C15" s="69" t="n"/>
+      <c r="D15" s="69" t="n"/>
       <c r="E15" s="15" t="inlineStr">
         <is>
           <t>Capacity Training</t>
@@ -3289,7 +3297,7 @@
       </c>
       <c r="K15" s="10" t="n"/>
       <c r="L15" s="10" t="n"/>
-      <c r="M15" s="68" t="n"/>
+      <c r="M15" s="70" t="n"/>
       <c r="N15" s="10" t="n"/>
       <c r="O15" t="inlineStr">
         <is>
@@ -3303,10 +3311,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="68" t="n"/>
-      <c r="B16" s="68" t="n"/>
-      <c r="C16" s="68" t="n"/>
-      <c r="D16" s="68" t="n"/>
+      <c r="A16" s="70" t="n"/>
+      <c r="B16" s="70" t="n"/>
+      <c r="C16" s="70" t="n"/>
+      <c r="D16" s="70" t="n"/>
       <c r="E16" s="15" t="inlineStr">
         <is>
           <t>Entrepreneurship Training</t>
@@ -4053,288 +4061,288 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="74" t="inlineStr">
+      <c r="A1" s="71" t="inlineStr">
         <is>
           <t>Beneficiary Category</t>
         </is>
       </c>
-      <c r="B1" s="74" t="inlineStr">
+      <c r="B1" s="71" t="inlineStr">
         <is>
           <t>Indicator</t>
         </is>
       </c>
     </row>
     <row r="2" ht="45.75" customHeight="1">
-      <c r="A2" s="75" t="inlineStr">
+      <c r="A2" s="72" t="inlineStr">
         <is>
           <t>Electricity Access</t>
         </is>
       </c>
-      <c r="B2" s="75" t="inlineStr">
+      <c r="B2" s="72" t="inlineStr">
         <is>
           <t>Number of people, disaggregated by sex, who gain access to clean electricity (direct access to electricity, lighting, cooling, etc.).</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="75" t="inlineStr">
+      <c r="A3" s="72" t="inlineStr">
         <is>
           <t>Energy (MW added)</t>
         </is>
       </c>
-      <c r="B3" s="75" t="inlineStr">
+      <c r="B3" s="72" t="inlineStr">
         <is>
           <t>Installed renewable or clean-energy power capacity added, in MW.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30.75" customHeight="1">
-      <c r="A4" s="75" t="inlineStr">
+      <c r="A4" s="72" t="inlineStr">
         <is>
           <t>Energy Storage (MW)</t>
         </is>
       </c>
-      <c r="B4" s="75" t="inlineStr">
+      <c r="B4" s="72" t="inlineStr">
         <is>
           <t>Installed energy storage power capacity added, in MW.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30.75" customHeight="1">
-      <c r="A5" s="75" t="inlineStr">
+      <c r="A5" s="72" t="inlineStr">
         <is>
           <t>Clean Cooking</t>
         </is>
       </c>
-      <c r="B5" s="75" t="inlineStr">
+      <c r="B5" s="72" t="inlineStr">
         <is>
           <t>Number of people who gain access to clean cooking (direct access to clean cook stoves, clean fuels, biomass, etc.).</t>
         </is>
       </c>
     </row>
     <row r="6" ht="91.5" customHeight="1">
-      <c r="A6" s="75" t="inlineStr">
+      <c r="A6" s="72" t="inlineStr">
         <is>
           <t>Clean Heating</t>
         </is>
       </c>
-      <c r="B6" s="75" t="inlineStr">
+      <c r="B6" s="72" t="inlineStr">
         <is>
           <t>Number of people who gain access to clean heating (direct access to clean electric heaters, clean fuels, etc.).</t>
         </is>
       </c>
     </row>
     <row r="7" ht="45.75" customHeight="1">
-      <c r="A7" s="75" t="inlineStr">
+      <c r="A7" s="72" t="inlineStr">
         <is>
           <t>Agriculture and Food System</t>
         </is>
       </c>
-      <c r="B7" s="75" t="inlineStr">
+      <c r="B7" s="72" t="inlineStr">
         <is>
           <t>Number of people who gain access to clean, affordable, and sustainable energy for agricultural and food-system activities.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="45.75" customHeight="1">
-      <c r="A8" s="75" t="inlineStr">
+      <c r="A8" s="72" t="inlineStr">
         <is>
           <t>Health Services</t>
         </is>
       </c>
-      <c r="B8" s="75" t="inlineStr">
+      <c r="B8" s="72" t="inlineStr">
         <is>
           <t>Number of people who gain access to health care facilities through clean energy systems.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="45.75" customHeight="1">
-      <c r="A9" s="75" t="inlineStr">
+      <c r="A9" s="72" t="inlineStr">
         <is>
           <t>Water Services</t>
         </is>
       </c>
-      <c r="B9" s="75" t="inlineStr">
+      <c r="B9" s="72" t="inlineStr">
         <is>
           <t>Number of people who gain access to water services through clean energy systems.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30.75" customHeight="1">
-      <c r="A10" s="75" t="inlineStr">
+      <c r="A10" s="72" t="inlineStr">
         <is>
           <t>Education Services</t>
         </is>
       </c>
-      <c r="B10" s="75" t="inlineStr">
+      <c r="B10" s="72" t="inlineStr">
         <is>
           <t>Number of people who gain access to education services through clean energy systems, including students and teachers.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30.75" customHeight="1">
-      <c r="A11" s="75" t="inlineStr">
+      <c r="A11" s="72" t="inlineStr">
         <is>
           <t>Transportation and E-mobility Services</t>
         </is>
       </c>
-      <c r="B11" s="75" t="inlineStr">
+      <c r="B11" s="72" t="inlineStr">
         <is>
           <t>Number of people served or energy saved from transport and e-mobility interventions, such as electric vehicles or charging stations.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="45.75" customHeight="1">
-      <c r="A12" s="75" t="inlineStr">
+      <c r="A12" s="72" t="inlineStr">
         <is>
           <t>Energy Efficiency Services</t>
         </is>
       </c>
-      <c r="B12" s="75" t="inlineStr">
+      <c r="B12" s="72" t="inlineStr">
         <is>
           <t>Energy saved from energy-efficiency interventions, such as building or industrial efficiency.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30.75" customHeight="1">
-      <c r="A13" s="75" t="inlineStr">
+      <c r="A13" s="72" t="inlineStr">
         <is>
           <t>Energy Infrastructure Services</t>
         </is>
       </c>
-      <c r="B13" s="75" t="inlineStr">
+      <c r="B13" s="72" t="inlineStr">
         <is>
           <t>Number of people benefiting from energy infrastructure interventions, such as streetlights, transmission, and distribution lines.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="75" t="inlineStr">
+      <c r="A14" s="72" t="inlineStr">
         <is>
           <t>Other Energy Services</t>
         </is>
       </c>
-      <c r="B14" s="75" t="inlineStr">
+      <c r="B14" s="72" t="inlineStr">
         <is>
           <t>Access to other energy services not captured by the categories above.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30.75" customHeight="1">
-      <c r="A15" s="75" t="inlineStr">
+      <c r="A15" s="72" t="inlineStr">
         <is>
           <t>Financing support</t>
         </is>
       </c>
-      <c r="B15" s="75" t="inlineStr">
+      <c r="B15" s="72" t="inlineStr">
         <is>
           <t>Support for the development of the energy market ecosystem.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30.75" customHeight="1">
-      <c r="A16" s="75" t="inlineStr">
+      <c r="A16" s="72" t="inlineStr">
         <is>
           <t>Medium Enterprises</t>
         </is>
       </c>
-      <c r="B16" s="75" t="inlineStr">
+      <c r="B16" s="72" t="inlineStr">
         <is>
           <t>Support for the development of medium enterprises in the energy transition market.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30.75" customHeight="1">
-      <c r="A17" s="75" t="inlineStr">
+      <c r="A17" s="72" t="inlineStr">
         <is>
           <t>Small Enterprises</t>
         </is>
       </c>
-      <c r="B17" s="75" t="inlineStr">
+      <c r="B17" s="72" t="inlineStr">
         <is>
           <t>Support for the development of small enterprises in the energy transition market.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="30.75" customHeight="1">
-      <c r="A18" s="75" t="inlineStr">
+      <c r="A18" s="72" t="inlineStr">
         <is>
           <t>Capacity Building Training</t>
         </is>
       </c>
-      <c r="B18" s="75" t="inlineStr">
+      <c r="B18" s="72" t="inlineStr">
         <is>
           <t>Number of people benefiting from training on energy business, energy finance, or related implementation capacity.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="76.5" customHeight="1">
-      <c r="A19" s="75" t="inlineStr">
+      <c r="A19" s="72" t="inlineStr">
         <is>
           <t>Entrepreneurship Training</t>
         </is>
       </c>
-      <c r="B19" s="75" t="inlineStr">
+      <c r="B19" s="72" t="inlineStr">
         <is>
           <t>Training for enterprises on the energy business, assumed to result in direct beneficiaries.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="30.75" customHeight="1">
-      <c r="A20" s="75" t="inlineStr">
+      <c r="A20" s="72" t="inlineStr">
         <is>
           <t>Market Intervention</t>
         </is>
       </c>
-      <c r="B20" s="75" t="inlineStr">
+      <c r="B20" s="72" t="inlineStr">
         <is>
           <t>Volume of investment leveraged or barriers removed for clean, reliable, affordable, and sustainable energy solutions.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="45.75" customHeight="1">
-      <c r="A21" s="75" t="inlineStr">
+      <c r="A21" s="72" t="inlineStr">
         <is>
           <t>Campaign Participant</t>
         </is>
       </c>
-      <c r="B21" s="75" t="inlineStr">
+      <c r="B21" s="72" t="inlineStr">
         <is>
           <t>Individuals who participate in advocacy or awareness campaigns on energy.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="30.75" customHeight="1">
-      <c r="A22" s="75" t="inlineStr">
+      <c r="A22" s="72" t="inlineStr">
         <is>
           <t>Policy or Regulatory Framework</t>
         </is>
       </c>
-      <c r="B22" s="75" t="inlineStr">
+      <c r="B22" s="72" t="inlineStr">
         <is>
           <t>Policies, regulations, strategies, plans, or frameworks developed, approved, implemented, or strengthened.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="75" t="inlineStr">
+      <c r="A23" s="72" t="inlineStr">
         <is>
           <t>GHG Emissions Reduction</t>
         </is>
       </c>
-      <c r="B23" s="75" t="inlineStr">
+      <c r="B23" s="72" t="inlineStr">
         <is>
           <t>Greenhouse gas emissions reduced or mitigated, in tCO2e.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="75" t="inlineStr">
+      <c r="A24" s="72" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="B24" s="75" t="inlineStr">
+      <c r="B24" s="72" t="inlineStr">
         <is>
           <t>Energy-related output that does not fit the standard categories above.</t>
         </is>
